--- a/countries/lu/2005-2009.xlsx
+++ b/countries/lu/2005-2009.xlsx
@@ -6779,22 +6779,22 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>D040</t>
+          <t>D045</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Rubella</t>
+          <t>Echinococcosis</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>风疹</t>
+          <t>包虫病</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Parasitic</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -6818,7 +6818,7 @@
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_RUBE_ANNUAL</t>
+          <t>SER_LU_ECDC_ECHI_ANNUAL</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6838,7 +6838,7 @@
       </c>
       <c r="AS44" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_RUBE_ANNUAL</t>
+          <t>SER_LU_ECDC_ECHI_ANNUAL</t>
         </is>
       </c>
       <c r="AT44" t="n">
@@ -6923,22 +6923,22 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>D045</t>
+          <t>D059</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Echinococcosis</t>
+          <t>Yellow fever</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>包虫病</t>
+          <t>黄热病</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Parasitic</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -6962,7 +6962,7 @@
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_ECHI_ANNUAL</t>
+          <t>SER_LU_ECDC_YELF_ANNUAL</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6982,7 +6982,7 @@
       </c>
       <c r="AS45" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_ECHI_ANNUAL</t>
+          <t>SER_LU_ECDC_YELF_ANNUAL</t>
         </is>
       </c>
       <c r="AT45" t="n">
@@ -7067,22 +7067,22 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>D059</t>
+          <t>D085</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Yellow fever</t>
+          <t>Toxoplasmosis</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>黄热病</t>
+          <t>弓形体病</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Parasitic</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -7106,7 +7106,7 @@
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_YELF_ANNUAL</t>
+          <t>SER_LU_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -7126,7 +7126,7 @@
       </c>
       <c r="AS46" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_YELF_ANNUAL</t>
+          <t>SER_LU_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT46" t="n">
@@ -7211,22 +7211,22 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>D085</t>
+          <t>D091</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Toxoplasmosis</t>
+          <t>Botulism</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>弓形体病</t>
+          <t>肉毒杆菌中毒</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Parasitic</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -7250,7 +7250,7 @@
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_TOXO_ANNUAL</t>
+          <t>SER_LU_ECDC_BOTU_ANNUAL</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -7270,7 +7270,7 @@
       </c>
       <c r="AS47" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_TOXO_ANNUAL</t>
+          <t>SER_LU_ECDC_BOTU_ANNUAL</t>
         </is>
       </c>
       <c r="AT47" t="n">
@@ -7355,17 +7355,17 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>D091</t>
+          <t>D092</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Botulism</t>
+          <t>Campylobacteriosis</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>肉毒杆菌中毒</t>
+          <t>弯曲杆菌病</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -7384,17 +7384,17 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>366</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>366</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>76.20713348741333</v>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_BOTU_ANNUAL</t>
+          <t>SER_LU_ECDC_CAMP_ANNUAL</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -7414,7 +7414,7 @@
       </c>
       <c r="AS48" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_BOTU_ANNUAL</t>
+          <t>SER_LU_ECDC_CAMP_ANNUAL</t>
         </is>
       </c>
       <c r="AT48" t="n">
@@ -7499,22 +7499,22 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>D092</t>
+          <t>D096</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Campylobacteriosis</t>
+          <t>Cryptosporidiosis</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>弯曲杆菌病</t>
+          <t>隐孢子虫病</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Parasitic</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -7528,17 +7528,17 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>366</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
-        <v>366</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>76.20713348741333</v>
+        <v>0</v>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_CAMP_ANNUAL</t>
+          <t>SER_LU_ECDC_CRYP_ANNUAL</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -7558,7 +7558,7 @@
       </c>
       <c r="AS49" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_CAMP_ANNUAL</t>
+          <t>SER_LU_ECDC_CRYP_ANNUAL</t>
         </is>
       </c>
       <c r="AT49" t="n">
@@ -7643,17 +7643,17 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>D096</t>
+          <t>D099</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Cryptosporidiosis</t>
+          <t>Giardiasis</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>隐孢子虫病</t>
+          <t>贾第虫病</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -7682,7 +7682,7 @@
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_CRYP_ANNUAL</t>
+          <t>SER_LU_ECDC_GIAR_ANNUAL</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -7702,7 +7702,7 @@
       </c>
       <c r="AS50" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_CRYP_ANNUAL</t>
+          <t>SER_LU_ECDC_GIAR_ANNUAL</t>
         </is>
       </c>
       <c r="AT50" t="n">
@@ -7787,22 +7787,22 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>D099</t>
+          <t>D100</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Giardiasis</t>
+          <t>Haemophilus influenzae</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>贾第虫病</t>
+          <t>流感嗜血杆菌</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Parasitic</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -7816,17 +7816,17 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>0.2082162117142441</v>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_GIAR_ANNUAL</t>
+          <t>SER_LU_ECDC_HAEINF_ANNUAL</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="AS51" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_GIAR_ANNUAL</t>
+          <t>SER_LU_ECDC_HAEINF_ANNUAL</t>
         </is>
       </c>
       <c r="AT51" t="n">
@@ -7931,17 +7931,17 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>D100</t>
+          <t>D105</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Haemophilus influenzae</t>
+          <t>Shigellosis</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>流感嗜血杆菌</t>
+          <t>志贺菌病</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -7960,17 +7960,17 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="O52" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="R52" t="n">
-        <v>0.2082162117142441</v>
+        <v>2.08216211714244</v>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_HAEINF_ANNUAL</t>
+          <t>SER_LU_ECDC_SHIG_ANNUAL</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7990,7 +7990,7 @@
       </c>
       <c r="AS52" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_HAEINF_ANNUAL</t>
+          <t>SER_LU_ECDC_SHIG_ANNUAL</t>
         </is>
       </c>
       <c r="AT52" t="n">
@@ -8075,17 +8075,17 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>D105</t>
+          <t>D107</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Shigellosis</t>
+          <t>Legionellosis</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>志贺菌病</t>
+          <t>军团菌病</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -8104,17 +8104,17 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="O53" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="R53" t="n">
-        <v>2.08216211714244</v>
+        <v>1.04108105857122</v>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_SHIG_ANNUAL</t>
+          <t>SER_LU_ECDC_LEGI_ANNUAL</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -8134,7 +8134,7 @@
       </c>
       <c r="AS53" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_SHIG_ANNUAL</t>
+          <t>SER_LU_ECDC_LEGI_ANNUAL</t>
         </is>
       </c>
       <c r="AT53" t="n">
@@ -8219,17 +8219,17 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>D107</t>
+          <t>D108</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Legionellosis</t>
+          <t>Listeriosis</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>军团菌病</t>
+          <t>李斯特菌病</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -8248,17 +8248,17 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O54" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R54" t="n">
-        <v>1.04108105857122</v>
+        <v>1.249297270285464</v>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_LEGI_ANNUAL</t>
+          <t>SER_LU_ECDC_LIST_ANNUAL</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -8278,7 +8278,7 @@
       </c>
       <c r="AS54" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_LEGI_ANNUAL</t>
+          <t>SER_LU_ECDC_LIST_ANNUAL</t>
         </is>
       </c>
       <c r="AT54" t="n">
@@ -8363,17 +8363,17 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>D108</t>
+          <t>D110</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Listeriosis</t>
+          <t>Meningococcal disease</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>李斯特菌病</t>
+          <t>脑膜炎球菌病</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -8392,17 +8392,17 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O55" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="R55" t="n">
-        <v>1.249297270285464</v>
+        <v>0.4164324234284881</v>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_LIST_ANNUAL</t>
+          <t>SER_LU_ECDC_MENI_ANNUAL</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -8422,7 +8422,7 @@
       </c>
       <c r="AS55" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_LIST_ANNUAL</t>
+          <t>SER_LU_ECDC_MENI_ANNUAL</t>
         </is>
       </c>
       <c r="AT55" t="n">
@@ -8507,17 +8507,17 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>D110</t>
+          <t>D114</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Meningococcal disease</t>
+          <t>Salmonellosis</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>脑膜炎球菌病</t>
+          <t>沙门氏菌病</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -8536,17 +8536,17 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>2</v>
+        <v>163</v>
       </c>
       <c r="O56" t="n">
-        <v>2</v>
+        <v>163</v>
       </c>
       <c r="R56" t="n">
-        <v>0.4164324234284881</v>
+        <v>33.93924250942178</v>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_MENI_ANNUAL</t>
+          <t>SER_LU_ECDC_SALM_ANNUAL</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -8566,7 +8566,7 @@
       </c>
       <c r="AS56" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_MENI_ANNUAL</t>
+          <t>SER_LU_ECDC_SALM_ANNUAL</t>
         </is>
       </c>
       <c r="AT56" t="n">
@@ -8651,17 +8651,17 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>D114</t>
+          <t>D115</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Salmonellosis</t>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>沙门氏菌病</t>
+          <t>产志贺毒素大肠杆菌感染</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -8680,17 +8680,17 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>163</v>
+        <v>1</v>
       </c>
       <c r="O57" t="n">
-        <v>163</v>
+        <v>1</v>
       </c>
       <c r="R57" t="n">
-        <v>33.93924250942178</v>
+        <v>0.2082162117142441</v>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_SALM_ANNUAL</t>
+          <t>SER_LU_ECDC_STEC_ANNUAL</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -8710,7 +8710,7 @@
       </c>
       <c r="AS57" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_SALM_ANNUAL</t>
+          <t>SER_LU_ECDC_STEC_ANNUAL</t>
         </is>
       </c>
       <c r="AT57" t="n">
@@ -8795,17 +8795,17 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>D115</t>
+          <t>D120</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Shiga toxin-producing Escherichia coli infection</t>
+          <t>Tetanus</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>产志贺毒素大肠杆菌感染</t>
+          <t>破伤风</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -8824,17 +8824,17 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>0.2082162117142441</v>
+        <v>0</v>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_STEC_ANNUAL</t>
+          <t>SER_LU_ECDC_TETA_ANNUAL</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AS58" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_STEC_ANNUAL</t>
+          <t>SER_LU_ECDC_TETA_ANNUAL</t>
         </is>
       </c>
       <c r="AT58" t="n">
@@ -8939,22 +8939,22 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>D120</t>
+          <t>D122</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Tetanus</t>
+          <t>Trichinellosis</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>破伤风</t>
+          <t>旋毛虫病</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Parasitic</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -8978,7 +8978,7 @@
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_TETA_ANNUAL</t>
+          <t>SER_LU_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -8998,7 +8998,7 @@
       </c>
       <c r="AS59" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_TETA_ANNUAL</t>
+          <t>SER_LU_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AT59" t="n">
@@ -9083,22 +9083,22 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>D122</t>
+          <t>D144</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Trichinellosis</t>
+          <t>Creutzfeldt-Jakob disease</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>旋毛虫病</t>
+          <t>克雅氏病</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Parasitic</t>
+          <t>Prion</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -9122,7 +9122,7 @@
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_TRIC_ANNUAL</t>
+          <t>SER_LU_ECDC_VCJD_ANNUAL</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -9142,7 +9142,7 @@
       </c>
       <c r="AS60" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_TRIC_ANNUAL</t>
+          <t>SER_LU_ECDC_VCJD_ANNUAL</t>
         </is>
       </c>
       <c r="AT60" t="n">
@@ -9227,22 +9227,22 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>D144</t>
+          <t>D155</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Creutzfeldt-Jakob disease</t>
+          <t>Yersiniosis</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>克雅氏病</t>
+          <t>耶尔森菌病</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Prion</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -9256,17 +9256,17 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="O61" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>4.58075665771337</v>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_VCJD_ANNUAL</t>
+          <t>SER_LU_ECDC_YERS_ANNUAL</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -9286,7 +9286,7 @@
       </c>
       <c r="AS61" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_VCJD_ANNUAL</t>
+          <t>SER_LU_ECDC_YERS_ANNUAL</t>
         </is>
       </c>
       <c r="AT61" t="n">
@@ -9371,22 +9371,22 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>D155</t>
+          <t>D162</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Yersiniosis</t>
+          <t>HIV infection</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>耶尔森菌病</t>
+          <t>人类免疫缺乏病毒感染</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -9400,17 +9400,17 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>22</v>
+        <v>100</v>
       </c>
       <c r="O62" t="n">
-        <v>22</v>
+        <v>100</v>
       </c>
       <c r="R62" t="n">
-        <v>4.58075665771337</v>
+        <v>20.82162117142441</v>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_YERS_ANNUAL</t>
+          <t>SER_LU_ECDC_HIV_INFECTION_ANNUAL</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -9430,7 +9430,7 @@
       </c>
       <c r="AS62" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_YERS_ANNUAL</t>
+          <t>SER_LU_ECDC_HIV_INFECTION_ANNUAL</t>
         </is>
       </c>
       <c r="AT62" t="n">
@@ -9515,46 +9515,46 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>D162</t>
+          <t>D002</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>HIV infection</t>
+          <t>Cholera</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>人类免疫缺乏病毒感染</t>
+          <t>霍乱</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>2007-01-01</t>
+          <t>2008-01-01</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>2007-01</t>
+          <t>2008-01</t>
         </is>
       </c>
       <c r="N63" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>20.82162117142441</v>
+        <v>0</v>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_HIV_INFECTION_ANNUAL</t>
+          <t>SER_LU_ECDC_CHOL_ANNUAL</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -9574,7 +9574,7 @@
       </c>
       <c r="AS63" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_HIV_INFECTION_ANNUAL</t>
+          <t>SER_LU_ECDC_CHOL_ANNUAL</t>
         </is>
       </c>
       <c r="AT63" t="n">
@@ -9659,22 +9659,22 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>D002</t>
+          <t>D005</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Cholera</t>
+          <t>AIDS</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>霍乱</t>
+          <t>艾滋病</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -9688,17 +9688,17 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="O64" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>3.067544256994768</v>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_CHOL_ANNUAL</t>
+          <t>SER_LU_ECDC_AIDS_ANNUAL</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -9718,7 +9718,7 @@
       </c>
       <c r="AS64" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_CHOL_ANNUAL</t>
+          <t>SER_LU_ECDC_AIDS_ANNUAL</t>
         </is>
       </c>
       <c r="AT64" t="n">
@@ -9803,17 +9803,17 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>D005</t>
+          <t>D007</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>AIDS</t>
+          <t>Hepatitis A</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>艾滋病</t>
+          <t>甲型肝炎</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -9832,17 +9832,17 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="O65" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="R65" t="n">
-        <v>3.067544256994768</v>
+        <v>0.6135088513989535</v>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_AIDS_ANNUAL</t>
+          <t>SER_LU_ECDC_HEPA_ANNUAL</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -9862,7 +9862,7 @@
       </c>
       <c r="AS65" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_AIDS_ANNUAL</t>
+          <t>SER_LU_ECDC_HEPA_ANNUAL</t>
         </is>
       </c>
       <c r="AT65" t="n">
@@ -9947,17 +9947,17 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>D007</t>
+          <t>D009</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Hepatitis A</t>
+          <t>Hepatitis C</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>甲型肝炎</t>
+          <t>丙型肝炎</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -9976,17 +9976,17 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>3</v>
+        <v>58</v>
       </c>
       <c r="O66" t="n">
-        <v>3</v>
+        <v>58</v>
       </c>
       <c r="R66" t="n">
-        <v>0.6135088513989535</v>
+        <v>11.86117112704644</v>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_HEPA_ANNUAL</t>
+          <t>SER_LU_ECDC_HEPC_ANNUAL</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -10006,7 +10006,7 @@
       </c>
       <c r="AS66" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_HEPA_ANNUAL</t>
+          <t>SER_LU_ECDC_HEPC_ANNUAL</t>
         </is>
       </c>
       <c r="AT66" t="n">
@@ -10091,17 +10091,17 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>D009</t>
+          <t>D017</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Hepatitis C</t>
+          <t>Measles</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>丙型肝炎</t>
+          <t>麻疹</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -10120,17 +10120,17 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>11.86117112704644</v>
+        <v>0</v>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_HEPC_ANNUAL</t>
+          <t>SER_LU_ECDC_MEAS_ANNUAL</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -10150,7 +10150,7 @@
       </c>
       <c r="AS67" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_HEPC_ANNUAL</t>
+          <t>SER_LU_ECDC_MEAS_ANNUAL</t>
         </is>
       </c>
       <c r="AT67" t="n">
@@ -10235,17 +10235,17 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>D017</t>
+          <t>D019</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Measles</t>
+          <t>Rabies</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>麻疹</t>
+          <t>狂犬病</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -10274,7 +10274,7 @@
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_MEAS_ANNUAL</t>
+          <t>SER_LU_ECDC_RABI_ANNUAL</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -10294,7 +10294,7 @@
       </c>
       <c r="AS68" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_MEAS_ANNUAL</t>
+          <t>SER_LU_ECDC_RABI_ANNUAL</t>
         </is>
       </c>
       <c r="AT68" t="n">
@@ -10379,17 +10379,17 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>D019</t>
+          <t>D021</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Rabies</t>
+          <t>Dengue</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>狂犬病</t>
+          <t>登革热</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -10418,7 +10418,7 @@
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_RABI_ANNUAL</t>
+          <t>SER_LU_ECDC_DENGUE_ANNUAL</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -10438,7 +10438,7 @@
       </c>
       <c r="AS69" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_RABI_ANNUAL</t>
+          <t>SER_LU_ECDC_DENGUE_ANNUAL</t>
         </is>
       </c>
       <c r="AT69" t="n">
@@ -10523,22 +10523,22 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>D021</t>
+          <t>D023</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Dengue</t>
+          <t>Anthrax</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>登革热</t>
+          <t>炭疽</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -10562,7 +10562,7 @@
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_DENGUE_ANNUAL</t>
+          <t>SER_LU_ECDC_ANTH_ANNUAL</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -10582,7 +10582,7 @@
       </c>
       <c r="AS70" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_DENGUE_ANNUAL</t>
+          <t>SER_LU_ECDC_ANTH_ANNUAL</t>
         </is>
       </c>
       <c r="AT70" t="n">
@@ -10667,17 +10667,17 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>D023</t>
+          <t>D025</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Anthrax</t>
+          <t>Tuberculosis</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>炭疽</t>
+          <t>肺结核</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -10696,17 +10696,17 @@
         </is>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="O71" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="R71" t="n">
-        <v>0</v>
+        <v>5.7260826130569</v>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_ANTH_ANNUAL</t>
+          <t>SER_LU_ECDC_TUBE_ANNUAL</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -10726,7 +10726,7 @@
       </c>
       <c r="AS71" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_ANTH_ANNUAL</t>
+          <t>SER_LU_ECDC_TUBE_ANNUAL</t>
         </is>
       </c>
       <c r="AT71" t="n">
@@ -10811,17 +10811,17 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>D025</t>
+          <t>D028</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Tuberculosis</t>
+          <t>Pertussis</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>肺结核</t>
+          <t>百日咳</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -10840,17 +10840,17 @@
         </is>
       </c>
       <c r="N72" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="O72" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="R72" t="n">
-        <v>5.7260826130569</v>
+        <v>0.4090059009326357</v>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_TUBE_ANNUAL</t>
+          <t>SER_LU_ECDC_PERT_ANNUAL</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -10870,7 +10870,7 @@
       </c>
       <c r="AS72" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_TUBE_ANNUAL</t>
+          <t>SER_LU_ECDC_PERT_ANNUAL</t>
         </is>
       </c>
       <c r="AT72" t="n">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>D028</t>
+          <t>D032</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Pertussis</t>
+          <t>Brucellosis</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>百日咳</t>
+          <t>布鲁氏菌病</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -10984,17 +10984,17 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>0.4090059009326357</v>
+        <v>0</v>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_PERT_ANNUAL</t>
+          <t>SER_LU_ECDC_BRUC_ANNUAL</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -11014,7 +11014,7 @@
       </c>
       <c r="AS73" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_PERT_ANNUAL</t>
+          <t>SER_LU_ECDC_BRUC_ANNUAL</t>
         </is>
       </c>
       <c r="AT73" t="n">
@@ -11099,17 +11099,17 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>D032</t>
+          <t>D033</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Brucellosis</t>
+          <t>Gonorrhea</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>布鲁氏菌病</t>
+          <t>淋病</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -11128,17 +11128,17 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="O74" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>3.681053108393721</v>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_BRUC_ANNUAL</t>
+          <t>SER_LU_ECDC_GONO_ANNUAL</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -11158,7 +11158,7 @@
       </c>
       <c r="AS74" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_BRUC_ANNUAL</t>
+          <t>SER_LU_ECDC_GONO_ANNUAL</t>
         </is>
       </c>
       <c r="AT74" t="n">
@@ -11243,17 +11243,17 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>D033</t>
+          <t>D035</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Gonorrhea</t>
+          <t>Leptospirosis</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>淋病</t>
+          <t>钩端螺旋体病</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -11272,17 +11272,17 @@
         </is>
       </c>
       <c r="N75" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="R75" t="n">
-        <v>3.681053108393721</v>
+        <v>0</v>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_GONO_ANNUAL</t>
+          <t>SER_LU_ECDC_LEPT_ANNUAL</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -11302,7 +11302,7 @@
       </c>
       <c r="AS75" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_GONO_ANNUAL</t>
+          <t>SER_LU_ECDC_LEPT_ANNUAL</t>
         </is>
       </c>
       <c r="AT75" t="n">
@@ -11387,22 +11387,22 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>D035</t>
+          <t>D037</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Leptospirosis</t>
+          <t>Malaria</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>钩端螺旋体病</t>
+          <t>疟疾</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Parasitic</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -11416,17 +11416,17 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O76" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R76" t="n">
-        <v>0</v>
+        <v>0.4090059009326357</v>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_LEPT_ANNUAL</t>
+          <t>SER_LU_ECDC_MALA_ANNUAL</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -11446,7 +11446,7 @@
       </c>
       <c r="AS76" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_LEPT_ANNUAL</t>
+          <t>SER_LU_ECDC_MALA_ANNUAL</t>
         </is>
       </c>
       <c r="AT76" t="n">
@@ -11531,22 +11531,22 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>D037</t>
+          <t>D039</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Malaria</t>
+          <t>Mumps</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>疟疾</t>
+          <t>流行性腮腺炎</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>Parasitic</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -11560,17 +11560,17 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="O77" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="R77" t="n">
-        <v>0.4090059009326357</v>
+        <v>5.7260826130569</v>
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_MALA_ANNUAL</t>
+          <t>SER_LU_ECDC_MUMP_ANNUAL</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -11590,7 +11590,7 @@
       </c>
       <c r="AS77" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_MALA_ANNUAL</t>
+          <t>SER_LU_ECDC_MUMP_ANNUAL</t>
         </is>
       </c>
       <c r="AT77" t="n">
@@ -11675,22 +11675,22 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>D039</t>
+          <t>D045</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Mumps</t>
+          <t>Echinococcosis</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>流行性腮腺炎</t>
+          <t>包虫病</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Parasitic</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -11704,17 +11704,17 @@
         </is>
       </c>
       <c r="N78" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="R78" t="n">
-        <v>5.7260826130569</v>
+        <v>0</v>
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_MUMP_ANNUAL</t>
+          <t>SER_LU_ECDC_ECHI_ANNUAL</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -11734,7 +11734,7 @@
       </c>
       <c r="AS78" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_MUMP_ANNUAL</t>
+          <t>SER_LU_ECDC_ECHI_ANNUAL</t>
         </is>
       </c>
       <c r="AT78" t="n">
@@ -11819,17 +11819,17 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>D040</t>
+          <t>D052</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Rubella</t>
+          <t>Chikungunya</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>风疹</t>
+          <t>基孔肯雅热</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -11858,7 +11858,7 @@
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_RUBE_ANNUAL</t>
+          <t>SER_LU_ECDC_CHIK_ANNUAL</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -11878,7 +11878,7 @@
       </c>
       <c r="AS79" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_RUBE_ANNUAL</t>
+          <t>SER_LU_ECDC_CHIK_ANNUAL</t>
         </is>
       </c>
       <c r="AT79" t="n">
@@ -11963,22 +11963,22 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>D045</t>
+          <t>D059</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Echinococcosis</t>
+          <t>Yellow fever</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>包虫病</t>
+          <t>黄热病</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>Parasitic</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -12002,7 +12002,7 @@
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_ECHI_ANNUAL</t>
+          <t>SER_LU_ECDC_YELF_ANNUAL</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -12022,7 +12022,7 @@
       </c>
       <c r="AS80" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_ECHI_ANNUAL</t>
+          <t>SER_LU_ECDC_YELF_ANNUAL</t>
         </is>
       </c>
       <c r="AT80" t="n">
@@ -12107,22 +12107,22 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>D052</t>
+          <t>D085</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Chikungunya</t>
+          <t>Toxoplasmosis</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>基孔肯雅热</t>
+          <t>弓形体病</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Parasitic</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -12146,7 +12146,7 @@
       </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_CHIK_ANNUAL</t>
+          <t>SER_LU_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="AS81" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_CHIK_ANNUAL</t>
+          <t>SER_LU_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT81" t="n">
@@ -12251,22 +12251,22 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>D059</t>
+          <t>D091</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Yellow fever</t>
+          <t>Botulism</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>黄热病</t>
+          <t>肉毒杆菌中毒</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -12280,17 +12280,17 @@
         </is>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R82" t="n">
-        <v>0</v>
+        <v>0.2045029504663179</v>
       </c>
       <c r="U82" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_YELF_ANNUAL</t>
+          <t>SER_LU_ECDC_BOTU_ANNUAL</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -12310,7 +12310,7 @@
       </c>
       <c r="AS82" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_YELF_ANNUAL</t>
+          <t>SER_LU_ECDC_BOTU_ANNUAL</t>
         </is>
       </c>
       <c r="AT82" t="n">
@@ -12395,22 +12395,22 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>D085</t>
+          <t>D092</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Toxoplasmosis</t>
+          <t>Campylobacteriosis</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>弓形体病</t>
+          <t>弯曲杆菌病</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>Parasitic</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -12424,17 +12424,17 @@
         </is>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>467</v>
       </c>
       <c r="O83" t="n">
-        <v>0</v>
+        <v>467</v>
       </c>
       <c r="R83" t="n">
-        <v>0</v>
+        <v>95.50287786777044</v>
       </c>
       <c r="U83" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_TOXO_ANNUAL</t>
+          <t>SER_LU_ECDC_CAMP_ANNUAL</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -12454,7 +12454,7 @@
       </c>
       <c r="AS83" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_TOXO_ANNUAL</t>
+          <t>SER_LU_ECDC_CAMP_ANNUAL</t>
         </is>
       </c>
       <c r="AT83" t="n">
@@ -12539,22 +12539,22 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>D091</t>
+          <t>D096</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Botulism</t>
+          <t>Cryptosporidiosis</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>肉毒杆菌中毒</t>
+          <t>隐孢子虫病</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Parasitic</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -12568,17 +12568,17 @@
         </is>
       </c>
       <c r="N84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R84" t="n">
-        <v>0.2045029504663179</v>
+        <v>0</v>
       </c>
       <c r="U84" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_BOTU_ANNUAL</t>
+          <t>SER_LU_ECDC_CRYP_ANNUAL</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -12598,7 +12598,7 @@
       </c>
       <c r="AS84" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_BOTU_ANNUAL</t>
+          <t>SER_LU_ECDC_CRYP_ANNUAL</t>
         </is>
       </c>
       <c r="AT84" t="n">
@@ -12683,22 +12683,22 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>D092</t>
+          <t>D099</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Campylobacteriosis</t>
+          <t>Giardiasis</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>弯曲杆菌病</t>
+          <t>贾第虫病</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Parasitic</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -12712,17 +12712,17 @@
         </is>
       </c>
       <c r="N85" t="n">
-        <v>467</v>
+        <v>1</v>
       </c>
       <c r="O85" t="n">
-        <v>467</v>
+        <v>1</v>
       </c>
       <c r="R85" t="n">
-        <v>95.50287786777044</v>
+        <v>0.2045029504663179</v>
       </c>
       <c r="U85" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_CAMP_ANNUAL</t>
+          <t>SER_LU_ECDC_GIAR_ANNUAL</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -12742,7 +12742,7 @@
       </c>
       <c r="AS85" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_CAMP_ANNUAL</t>
+          <t>SER_LU_ECDC_GIAR_ANNUAL</t>
         </is>
       </c>
       <c r="AT85" t="n">
@@ -12827,22 +12827,22 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>D096</t>
+          <t>D100</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Cryptosporidiosis</t>
+          <t>Haemophilus influenzae</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>隐孢子虫病</t>
+          <t>流感嗜血杆菌</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>Parasitic</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -12866,7 +12866,7 @@
       </c>
       <c r="U86" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_CRYP_ANNUAL</t>
+          <t>SER_LU_ECDC_HAEINF_ANNUAL</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -12886,7 +12886,7 @@
       </c>
       <c r="AS86" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_CRYP_ANNUAL</t>
+          <t>SER_LU_ECDC_HAEINF_ANNUAL</t>
         </is>
       </c>
       <c r="AT86" t="n">
@@ -12971,22 +12971,22 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>D099</t>
+          <t>D102</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Giardiasis</t>
+          <t>Hantavirus infection</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>贾第虫病</t>
+          <t>汉坦病毒感染</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>Parasitic</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -13000,17 +13000,17 @@
         </is>
       </c>
       <c r="N87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R87" t="n">
-        <v>0.2045029504663179</v>
+        <v>0</v>
       </c>
       <c r="U87" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_GIAR_ANNUAL</t>
+          <t>SER_LU_ECDC_HANTA_ANNUAL</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -13030,7 +13030,7 @@
       </c>
       <c r="AS87" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_GIAR_ANNUAL</t>
+          <t>SER_LU_ECDC_HANTA_ANNUAL</t>
         </is>
       </c>
       <c r="AT87" t="n">
@@ -13115,17 +13115,17 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>D100</t>
+          <t>D105</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Haemophilus influenzae</t>
+          <t>Shigellosis</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>流感嗜血杆菌</t>
+          <t>志贺菌病</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -13144,17 +13144,17 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="O88" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="R88" t="n">
-        <v>0</v>
+        <v>3.681053108393721</v>
       </c>
       <c r="U88" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_HAEINF_ANNUAL</t>
+          <t>SER_LU_ECDC_SHIG_ANNUAL</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -13174,7 +13174,7 @@
       </c>
       <c r="AS88" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_HAEINF_ANNUAL</t>
+          <t>SER_LU_ECDC_SHIG_ANNUAL</t>
         </is>
       </c>
       <c r="AT88" t="n">
@@ -13259,22 +13259,22 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>D102</t>
+          <t>D107</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Hantavirus infection</t>
+          <t>Legionellosis</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>汉坦病毒感染</t>
+          <t>军团菌病</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -13288,17 +13288,17 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O89" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R89" t="n">
-        <v>0</v>
+        <v>1.022514752331589</v>
       </c>
       <c r="U89" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_HANTA_ANNUAL</t>
+          <t>SER_LU_ECDC_LEGI_ANNUAL</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -13318,7 +13318,7 @@
       </c>
       <c r="AS89" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_HANTA_ANNUAL</t>
+          <t>SER_LU_ECDC_LEGI_ANNUAL</t>
         </is>
       </c>
       <c r="AT89" t="n">
@@ -13403,17 +13403,17 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>D105</t>
+          <t>D108</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Shigellosis</t>
+          <t>Listeriosis</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>志贺菌病</t>
+          <t>李斯特菌病</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -13432,17 +13432,17 @@
         </is>
       </c>
       <c r="N90" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="O90" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="R90" t="n">
-        <v>3.681053108393721</v>
+        <v>0.2045029504663179</v>
       </c>
       <c r="U90" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_SHIG_ANNUAL</t>
+          <t>SER_LU_ECDC_LIST_ANNUAL</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -13462,7 +13462,7 @@
       </c>
       <c r="AS90" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_SHIG_ANNUAL</t>
+          <t>SER_LU_ECDC_LIST_ANNUAL</t>
         </is>
       </c>
       <c r="AT90" t="n">
@@ -13547,17 +13547,17 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>D107</t>
+          <t>D110</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Legionellosis</t>
+          <t>Meningococcal disease</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>军团菌病</t>
+          <t>脑膜炎球菌病</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -13576,17 +13576,17 @@
         </is>
       </c>
       <c r="N91" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O91" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R91" t="n">
-        <v>1.022514752331589</v>
+        <v>0.4090059009326357</v>
       </c>
       <c r="U91" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_LEGI_ANNUAL</t>
+          <t>SER_LU_ECDC_MENI_ANNUAL</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -13606,7 +13606,7 @@
       </c>
       <c r="AS91" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_LEGI_ANNUAL</t>
+          <t>SER_LU_ECDC_MENI_ANNUAL</t>
         </is>
       </c>
       <c r="AT91" t="n">
@@ -13691,17 +13691,17 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>D108</t>
+          <t>D113</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Listeriosis</t>
+          <t>Q fever</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>李斯特菌病</t>
+          <t>Q热</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -13720,17 +13720,17 @@
         </is>
       </c>
       <c r="N92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R92" t="n">
-        <v>0.2045029504663179</v>
+        <v>0</v>
       </c>
       <c r="U92" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_LIST_ANNUAL</t>
+          <t>SER_LU_ECDC_QFEV_ANNUAL</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -13750,7 +13750,7 @@
       </c>
       <c r="AS92" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_LIST_ANNUAL</t>
+          <t>SER_LU_ECDC_QFEV_ANNUAL</t>
         </is>
       </c>
       <c r="AT92" t="n">
@@ -13835,17 +13835,17 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>D110</t>
+          <t>D114</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Meningococcal disease</t>
+          <t>Salmonellosis</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>脑膜炎球菌病</t>
+          <t>沙门氏菌病</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -13864,17 +13864,17 @@
         </is>
       </c>
       <c r="N93" t="n">
-        <v>2</v>
+        <v>153</v>
       </c>
       <c r="O93" t="n">
-        <v>2</v>
+        <v>153</v>
       </c>
       <c r="R93" t="n">
-        <v>0.4090059009326357</v>
+        <v>31.28895142134663</v>
       </c>
       <c r="U93" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_MENI_ANNUAL</t>
+          <t>SER_LU_ECDC_SALM_ANNUAL</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AS93" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_MENI_ANNUAL</t>
+          <t>SER_LU_ECDC_SALM_ANNUAL</t>
         </is>
       </c>
       <c r="AT93" t="n">
@@ -13979,17 +13979,17 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>D113</t>
+          <t>D115</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Q fever</t>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>Q热</t>
+          <t>产志贺毒素大肠杆菌感染</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -14008,17 +14008,17 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O94" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R94" t="n">
-        <v>0</v>
+        <v>0.8180118018652714</v>
       </c>
       <c r="U94" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_QFEV_ANNUAL</t>
+          <t>SER_LU_ECDC_STEC_ANNUAL</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -14038,7 +14038,7 @@
       </c>
       <c r="AS94" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_QFEV_ANNUAL</t>
+          <t>SER_LU_ECDC_STEC_ANNUAL</t>
         </is>
       </c>
       <c r="AT94" t="n">
@@ -14123,17 +14123,17 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>D114</t>
+          <t>D120</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Salmonellosis</t>
+          <t>Tetanus</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>沙门氏菌病</t>
+          <t>破伤风</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -14152,17 +14152,17 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>153</v>
+        <v>0</v>
       </c>
       <c r="O95" t="n">
-        <v>153</v>
+        <v>0</v>
       </c>
       <c r="R95" t="n">
-        <v>31.28895142134663</v>
+        <v>0</v>
       </c>
       <c r="U95" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_SALM_ANNUAL</t>
+          <t>SER_LU_ECDC_TETA_ANNUAL</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -14182,7 +14182,7 @@
       </c>
       <c r="AS95" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_SALM_ANNUAL</t>
+          <t>SER_LU_ECDC_TETA_ANNUAL</t>
         </is>
       </c>
       <c r="AT95" t="n">
@@ -14267,22 +14267,22 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>D115</t>
+          <t>D122</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Shiga toxin-producing Escherichia coli infection</t>
+          <t>Trichinellosis</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>产志贺毒素大肠杆菌感染</t>
+          <t>旋毛虫病</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Parasitic</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -14296,17 +14296,17 @@
         </is>
       </c>
       <c r="N96" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O96" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R96" t="n">
-        <v>0.8180118018652714</v>
+        <v>0</v>
       </c>
       <c r="U96" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_STEC_ANNUAL</t>
+          <t>SER_LU_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -14326,7 +14326,7 @@
       </c>
       <c r="AS96" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_STEC_ANNUAL</t>
+          <t>SER_LU_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AT96" t="n">
@@ -14411,17 +14411,17 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>D120</t>
+          <t>D123</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Tetanus</t>
+          <t>Tularemia</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>破伤风</t>
+          <t>土拉菌病</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -14450,7 +14450,7 @@
       </c>
       <c r="U97" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_TETA_ANNUAL</t>
+          <t>SER_LU_ECDC_TULA_ANNUAL</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -14470,7 +14470,7 @@
       </c>
       <c r="AS97" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_TETA_ANNUAL</t>
+          <t>SER_LU_ECDC_TULA_ANNUAL</t>
         </is>
       </c>
       <c r="AT97" t="n">
@@ -14555,22 +14555,22 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>D122</t>
+          <t>D127</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Trichinellosis</t>
+          <t>Viral hemorrhagic fevers</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>旋毛虫病</t>
+          <t>病毒性出血热</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>Parasitic</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -14594,7 +14594,7 @@
       </c>
       <c r="U98" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_TRIC_ANNUAL</t>
+          <t>SER_LU_ECDC_VHFOTH_ANNUAL</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -14614,7 +14614,7 @@
       </c>
       <c r="AS98" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_TRIC_ANNUAL</t>
+          <t>SER_LU_ECDC_VHFOTH_ANNUAL</t>
         </is>
       </c>
       <c r="AT98" t="n">
@@ -14699,22 +14699,22 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>D123</t>
+          <t>D128</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Tularemia</t>
+          <t>West Nile virus</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>土拉菌病</t>
+          <t>西尼罗病毒</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -14738,7 +14738,7 @@
       </c>
       <c r="U99" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_TULA_ANNUAL</t>
+          <t>SER_LU_ECDC_WNF_ANNUAL</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -14758,7 +14758,7 @@
       </c>
       <c r="AS99" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_TULA_ANNUAL</t>
+          <t>SER_LU_ECDC_WNF_ANNUAL</t>
         </is>
       </c>
       <c r="AT99" t="n">
@@ -14843,22 +14843,22 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>D127</t>
+          <t>D144</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Viral hemorrhagic fevers</t>
+          <t>Creutzfeldt-Jakob disease</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>病毒性出血热</t>
+          <t>克雅氏病</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Prion</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -14882,7 +14882,7 @@
       </c>
       <c r="U100" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_VHFOTH_ANNUAL</t>
+          <t>SER_LU_ECDC_VCJD_ANNUAL</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -14902,7 +14902,7 @@
       </c>
       <c r="AS100" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_VHFOTH_ANNUAL</t>
+          <t>SER_LU_ECDC_VCJD_ANNUAL</t>
         </is>
       </c>
       <c r="AT100" t="n">
@@ -14987,22 +14987,22 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>D128</t>
+          <t>D155</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>West Nile virus</t>
+          <t>Yersiniosis</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>西尼罗病毒</t>
+          <t>耶尔森菌病</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -15016,17 +15016,17 @@
         </is>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="O101" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="R101" t="n">
-        <v>0</v>
+        <v>3.476550157927404</v>
       </c>
       <c r="U101" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_WNF_ANNUAL</t>
+          <t>SER_LU_ECDC_YERS_ANNUAL</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -15046,7 +15046,7 @@
       </c>
       <c r="AS101" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_WNF_ANNUAL</t>
+          <t>SER_LU_ECDC_YERS_ANNUAL</t>
         </is>
       </c>
       <c r="AT101" t="n">
@@ -15131,22 +15131,22 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>D144</t>
+          <t>D162</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Creutzfeldt-Jakob disease</t>
+          <t>HIV infection</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>克雅氏病</t>
+          <t>人类免疫缺乏病毒感染</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>Prion</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -15160,17 +15160,17 @@
         </is>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="O102" t="n">
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="R102" t="n">
-        <v>0</v>
+        <v>24.33585110549182</v>
       </c>
       <c r="U102" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_VCJD_ANNUAL</t>
+          <t>SER_LU_ECDC_HIV_INFECTION_ANNUAL</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -15190,7 +15190,7 @@
       </c>
       <c r="AS102" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_VCJD_ANNUAL</t>
+          <t>SER_LU_ECDC_HIV_INFECTION_ANNUAL</t>
         </is>
       </c>
       <c r="AT102" t="n">
@@ -15275,22 +15275,22 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>D155</t>
+          <t>D173</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Yersiniosis</t>
+          <t>Rift Valley fever</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>耶尔森菌病</t>
+          <t>裂谷热</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -15304,17 +15304,17 @@
         </is>
       </c>
       <c r="N103" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="O103" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="R103" t="n">
-        <v>3.476550157927404</v>
+        <v>0</v>
       </c>
       <c r="U103" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_YERS_ANNUAL</t>
+          <t>SER_LU_ECDC_RIFT_ANNUAL</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -15334,7 +15334,7 @@
       </c>
       <c r="AS103" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_YERS_ANNUAL</t>
+          <t>SER_LU_ECDC_RIFT_ANNUAL</t>
         </is>
       </c>
       <c r="AT103" t="n">
@@ -15419,17 +15419,17 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>D162</t>
+          <t>D203</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>HIV infection</t>
+          <t>Crimean-Congo hemorrhagic fever</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>人类免疫缺乏病毒感染</t>
+          <t>克里米亚-刚果出血热</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -15448,17 +15448,17 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>119</v>
+        <v>0</v>
       </c>
       <c r="O104" t="n">
-        <v>119</v>
+        <v>0</v>
       </c>
       <c r="R104" t="n">
-        <v>24.33585110549182</v>
+        <v>0</v>
       </c>
       <c r="U104" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_HIV_INFECTION_ANNUAL</t>
+          <t>SER_LU_ECDC_CCHF_ANNUAL</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -15478,7 +15478,7 @@
       </c>
       <c r="AS104" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_HIV_INFECTION_ANNUAL</t>
+          <t>SER_LU_ECDC_CCHF_ANNUAL</t>
         </is>
       </c>
       <c r="AT104" t="n">
@@ -15563,32 +15563,32 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>D173</t>
+          <t>D002</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Rift Valley fever</t>
+          <t>Cholera</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>裂谷热</t>
+          <t>霍乱</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>2008-01-01</t>
+          <t>2009-01-01</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>2008-01</t>
+          <t>2009-01</t>
         </is>
       </c>
       <c r="N105" t="n">
@@ -15602,7 +15602,7 @@
       </c>
       <c r="U105" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_RIFT_ANNUAL</t>
+          <t>SER_LU_ECDC_CHOL_ANNUAL</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -15622,7 +15622,7 @@
       </c>
       <c r="AS105" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_RIFT_ANNUAL</t>
+          <t>SER_LU_ECDC_CHOL_ANNUAL</t>
         </is>
       </c>
       <c r="AT105" t="n">
@@ -15707,17 +15707,17 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>D203</t>
+          <t>D005</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Crimean-Congo hemorrhagic fever</t>
+          <t>AIDS</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>克里米亚-刚果出血热</t>
+          <t>艾滋病</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -15727,26 +15727,26 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>2008-01-01</t>
+          <t>2009-01-01</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>2008-01</t>
+          <t>2009-01</t>
         </is>
       </c>
       <c r="N106" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O106" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="R106" t="n">
-        <v>0</v>
+        <v>1.806552365429412</v>
       </c>
       <c r="U106" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_CCHF_ANNUAL</t>
+          <t>SER_LU_ECDC_AIDS_ANNUAL</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -15766,7 +15766,7 @@
       </c>
       <c r="AS106" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_CCHF_ANNUAL</t>
+          <t>SER_LU_ECDC_AIDS_ANNUAL</t>
         </is>
       </c>
       <c r="AT106" t="n">
@@ -15851,22 +15851,22 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>D002</t>
+          <t>D007</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Cholera</t>
+          <t>Hepatitis A</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>霍乱</t>
+          <t>甲型肝炎</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -15880,17 +15880,17 @@
         </is>
       </c>
       <c r="N107" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O107" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R107" t="n">
-        <v>0</v>
+        <v>1.00364020301634</v>
       </c>
       <c r="U107" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_CHOL_ANNUAL</t>
+          <t>SER_LU_ECDC_HEPA_ANNUAL</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -15910,7 +15910,7 @@
       </c>
       <c r="AS107" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_CHOL_ANNUAL</t>
+          <t>SER_LU_ECDC_HEPA_ANNUAL</t>
         </is>
       </c>
       <c r="AT107" t="n">
@@ -15995,17 +15995,17 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>D005</t>
+          <t>D009</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>AIDS</t>
+          <t>Hepatitis C</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>艾滋病</t>
+          <t>丙型肝炎</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -16024,17 +16024,17 @@
         </is>
       </c>
       <c r="N108" t="n">
-        <v>9</v>
+        <v>55</v>
       </c>
       <c r="O108" t="n">
-        <v>9</v>
+        <v>55</v>
       </c>
       <c r="R108" t="n">
-        <v>1.806552365429412</v>
+        <v>11.04004223317974</v>
       </c>
       <c r="U108" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_AIDS_ANNUAL</t>
+          <t>SER_LU_ECDC_HEPC_ANNUAL</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -16054,7 +16054,7 @@
       </c>
       <c r="AS108" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_AIDS_ANNUAL</t>
+          <t>SER_LU_ECDC_HEPC_ANNUAL</t>
         </is>
       </c>
       <c r="AT108" t="n">
@@ -16139,17 +16139,17 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>D007</t>
+          <t>D017</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Hepatitis A</t>
+          <t>Measles</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>甲型肝炎</t>
+          <t>麻疹</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -16168,17 +16168,17 @@
         </is>
       </c>
       <c r="N109" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O109" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R109" t="n">
-        <v>1.00364020301634</v>
+        <v>0</v>
       </c>
       <c r="U109" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_HEPA_ANNUAL</t>
+          <t>SER_LU_ECDC_MEAS_ANNUAL</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -16198,7 +16198,7 @@
       </c>
       <c r="AS109" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_HEPA_ANNUAL</t>
+          <t>SER_LU_ECDC_MEAS_ANNUAL</t>
         </is>
       </c>
       <c r="AT109" t="n">
@@ -16283,17 +16283,17 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>D009</t>
+          <t>D019</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Hepatitis C</t>
+          <t>Rabies</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>丙型肝炎</t>
+          <t>狂犬病</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -16312,17 +16312,17 @@
         </is>
       </c>
       <c r="N110" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="O110" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="R110" t="n">
-        <v>11.04004223317974</v>
+        <v>0</v>
       </c>
       <c r="U110" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_HEPC_ANNUAL</t>
+          <t>SER_LU_ECDC_RABI_ANNUAL</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -16342,7 +16342,7 @@
       </c>
       <c r="AS110" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_HEPC_ANNUAL</t>
+          <t>SER_LU_ECDC_RABI_ANNUAL</t>
         </is>
       </c>
       <c r="AT110" t="n">
@@ -16427,17 +16427,17 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>D017</t>
+          <t>D021</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Measles</t>
+          <t>Dengue</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>麻疹</t>
+          <t>登革热</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -16466,7 +16466,7 @@
       </c>
       <c r="U111" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_MEAS_ANNUAL</t>
+          <t>SER_LU_ECDC_DENGUE_ANNUAL</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -16486,7 +16486,7 @@
       </c>
       <c r="AS111" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_MEAS_ANNUAL</t>
+          <t>SER_LU_ECDC_DENGUE_ANNUAL</t>
         </is>
       </c>
       <c r="AT111" t="n">
@@ -16571,22 +16571,22 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>D019</t>
+          <t>D023</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Rabies</t>
+          <t>Anthrax</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>狂犬病</t>
+          <t>炭疽</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -16610,7 +16610,7 @@
       </c>
       <c r="U112" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_RABI_ANNUAL</t>
+          <t>SER_LU_ECDC_ANTH_ANNUAL</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -16630,7 +16630,7 @@
       </c>
       <c r="AS112" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_RABI_ANNUAL</t>
+          <t>SER_LU_ECDC_ANTH_ANNUAL</t>
         </is>
       </c>
       <c r="AT112" t="n">
@@ -16715,22 +16715,22 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>D021</t>
+          <t>D025</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Dengue</t>
+          <t>Tuberculosis</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>登革热</t>
+          <t>肺结核</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -16744,17 +16744,17 @@
         </is>
       </c>
       <c r="N113" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="O113" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="R113" t="n">
-        <v>0</v>
+        <v>5.419657096288238</v>
       </c>
       <c r="U113" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_DENGUE_ANNUAL</t>
+          <t>SER_LU_ECDC_TUBE_ANNUAL</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -16774,7 +16774,7 @@
       </c>
       <c r="AS113" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_DENGUE_ANNUAL</t>
+          <t>SER_LU_ECDC_TUBE_ANNUAL</t>
         </is>
       </c>
       <c r="AT113" t="n">
@@ -16859,17 +16859,17 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>D023</t>
+          <t>D028</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Anthrax</t>
+          <t>Pertussis</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>炭疽</t>
+          <t>百日咳</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -16888,17 +16888,17 @@
         </is>
       </c>
       <c r="N114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R114" t="n">
-        <v>0</v>
+        <v>0.200728040603268</v>
       </c>
       <c r="U114" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_ANTH_ANNUAL</t>
+          <t>SER_LU_ECDC_PERT_ANNUAL</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -16918,7 +16918,7 @@
       </c>
       <c r="AS114" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_ANTH_ANNUAL</t>
+          <t>SER_LU_ECDC_PERT_ANNUAL</t>
         </is>
       </c>
       <c r="AT114" t="n">
@@ -17003,17 +17003,17 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>D025</t>
+          <t>D032</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Tuberculosis</t>
+          <t>Brucellosis</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>肺结核</t>
+          <t>布鲁氏菌病</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -17032,17 +17032,17 @@
         </is>
       </c>
       <c r="N115" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="O115" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="R115" t="n">
-        <v>5.419657096288238</v>
+        <v>0</v>
       </c>
       <c r="U115" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_TUBE_ANNUAL</t>
+          <t>SER_LU_ECDC_BRUC_ANNUAL</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -17062,7 +17062,7 @@
       </c>
       <c r="AS115" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_TUBE_ANNUAL</t>
+          <t>SER_LU_ECDC_BRUC_ANNUAL</t>
         </is>
       </c>
       <c r="AT115" t="n">
@@ -17147,17 +17147,17 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>D028</t>
+          <t>D033</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Pertussis</t>
+          <t>Gonorrhea</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>百日咳</t>
+          <t>淋病</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -17176,17 +17176,17 @@
         </is>
       </c>
       <c r="N116" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="O116" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="R116" t="n">
-        <v>0.200728040603268</v>
+        <v>1.204368243619608</v>
       </c>
       <c r="U116" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_PERT_ANNUAL</t>
+          <t>SER_LU_ECDC_GONO_ANNUAL</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -17206,7 +17206,7 @@
       </c>
       <c r="AS116" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_PERT_ANNUAL</t>
+          <t>SER_LU_ECDC_GONO_ANNUAL</t>
         </is>
       </c>
       <c r="AT116" t="n">
@@ -17291,17 +17291,17 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>D032</t>
+          <t>D035</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Brucellosis</t>
+          <t>Leptospirosis</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>布鲁氏菌病</t>
+          <t>钩端螺旋体病</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -17330,7 +17330,7 @@
       </c>
       <c r="U117" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_BRUC_ANNUAL</t>
+          <t>SER_LU_ECDC_LEPT_ANNUAL</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -17350,7 +17350,7 @@
       </c>
       <c r="AS117" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_BRUC_ANNUAL</t>
+          <t>SER_LU_ECDC_LEPT_ANNUAL</t>
         </is>
       </c>
       <c r="AT117" t="n">
@@ -17435,22 +17435,22 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>D033</t>
+          <t>D037</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Gonorrhea</t>
+          <t>Malaria</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>淋病</t>
+          <t>疟疾</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Parasitic</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -17464,17 +17464,17 @@
         </is>
       </c>
       <c r="N118" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O118" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="R118" t="n">
-        <v>1.204368243619608</v>
+        <v>0.6021841218098042</v>
       </c>
       <c r="U118" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_GONO_ANNUAL</t>
+          <t>SER_LU_ECDC_MALA_ANNUAL</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -17494,7 +17494,7 @@
       </c>
       <c r="AS118" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_GONO_ANNUAL</t>
+          <t>SER_LU_ECDC_MALA_ANNUAL</t>
         </is>
       </c>
       <c r="AT118" t="n">
@@ -17579,22 +17579,22 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>D035</t>
+          <t>D039</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Leptospirosis</t>
+          <t>Mumps</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>钩端螺旋体病</t>
+          <t>流行性腮腺炎</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -17608,17 +17608,17 @@
         </is>
       </c>
       <c r="N119" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="O119" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="R119" t="n">
-        <v>0</v>
+        <v>5.018201015081701</v>
       </c>
       <c r="U119" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_LEPT_ANNUAL</t>
+          <t>SER_LU_ECDC_MUMP_ANNUAL</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -17638,7 +17638,7 @@
       </c>
       <c r="AS119" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_LEPT_ANNUAL</t>
+          <t>SER_LU_ECDC_MUMP_ANNUAL</t>
         </is>
       </c>
       <c r="AT119" t="n">
@@ -17723,17 +17723,17 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>D037</t>
+          <t>D045</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Malaria</t>
+          <t>Echinococcosis</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>疟疾</t>
+          <t>包虫病</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -17752,17 +17752,17 @@
         </is>
       </c>
       <c r="N120" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O120" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R120" t="n">
-        <v>0.6021841218098042</v>
+        <v>0</v>
       </c>
       <c r="U120" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_MALA_ANNUAL</t>
+          <t>SER_LU_ECDC_ECHI_ANNUAL</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -17782,7 +17782,7 @@
       </c>
       <c r="AS120" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_MALA_ANNUAL</t>
+          <t>SER_LU_ECDC_ECHI_ANNUAL</t>
         </is>
       </c>
       <c r="AT120" t="n">
@@ -17867,17 +17867,17 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>D039</t>
+          <t>D052</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Mumps</t>
+          <t>Chikungunya</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>流行性腮腺炎</t>
+          <t>基孔肯雅热</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -17896,17 +17896,17 @@
         </is>
       </c>
       <c r="N121" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="O121" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="R121" t="n">
-        <v>5.018201015081701</v>
+        <v>0</v>
       </c>
       <c r="U121" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_MUMP_ANNUAL</t>
+          <t>SER_LU_ECDC_CHIK_ANNUAL</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -17926,7 +17926,7 @@
       </c>
       <c r="AS121" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_MUMP_ANNUAL</t>
+          <t>SER_LU_ECDC_CHIK_ANNUAL</t>
         </is>
       </c>
       <c r="AT121" t="n">
@@ -18011,17 +18011,17 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>D040</t>
+          <t>D059</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Rubella</t>
+          <t>Yellow fever</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>风疹</t>
+          <t>黄热病</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -18050,7 +18050,7 @@
       </c>
       <c r="U122" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_RUBE_ANNUAL</t>
+          <t>SER_LU_ECDC_YELF_ANNUAL</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -18070,7 +18070,7 @@
       </c>
       <c r="AS122" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_RUBE_ANNUAL</t>
+          <t>SER_LU_ECDC_YELF_ANNUAL</t>
         </is>
       </c>
       <c r="AT122" t="n">
@@ -18155,17 +18155,17 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>D045</t>
+          <t>D085</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Echinococcosis</t>
+          <t>Toxoplasmosis</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>包虫病</t>
+          <t>弓形体病</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -18194,7 +18194,7 @@
       </c>
       <c r="U123" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_ECHI_ANNUAL</t>
+          <t>SER_LU_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -18214,7 +18214,7 @@
       </c>
       <c r="AS123" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_ECHI_ANNUAL</t>
+          <t>SER_LU_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT123" t="n">
@@ -18299,22 +18299,22 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>D052</t>
+          <t>D091</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Chikungunya</t>
+          <t>Botulism</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>基孔肯雅热</t>
+          <t>肉毒杆菌中毒</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -18338,7 +18338,7 @@
       </c>
       <c r="U124" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_CHIK_ANNUAL</t>
+          <t>SER_LU_ECDC_BOTU_ANNUAL</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -18358,7 +18358,7 @@
       </c>
       <c r="AS124" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_CHIK_ANNUAL</t>
+          <t>SER_LU_ECDC_BOTU_ANNUAL</t>
         </is>
       </c>
       <c r="AT124" t="n">
@@ -18443,22 +18443,22 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>D059</t>
+          <t>D092</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Yellow fever</t>
+          <t>Campylobacteriosis</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>黄热病</t>
+          <t>弯曲杆菌病</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -18472,17 +18472,17 @@
         </is>
       </c>
       <c r="N125" t="n">
-        <v>0</v>
+        <v>523</v>
       </c>
       <c r="O125" t="n">
-        <v>0</v>
+        <v>523</v>
       </c>
       <c r="R125" t="n">
-        <v>0</v>
+        <v>104.9807652355092</v>
       </c>
       <c r="U125" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_YELF_ANNUAL</t>
+          <t>SER_LU_ECDC_CAMP_ANNUAL</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -18502,7 +18502,7 @@
       </c>
       <c r="AS125" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_YELF_ANNUAL</t>
+          <t>SER_LU_ECDC_CAMP_ANNUAL</t>
         </is>
       </c>
       <c r="AT125" t="n">
@@ -18587,17 +18587,17 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>D085</t>
+          <t>D096</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Toxoplasmosis</t>
+          <t>Cryptosporidiosis</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>弓形体病</t>
+          <t>隐孢子虫病</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
@@ -18626,7 +18626,7 @@
       </c>
       <c r="U126" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_TOXO_ANNUAL</t>
+          <t>SER_LU_ECDC_CRYP_ANNUAL</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -18646,7 +18646,7 @@
       </c>
       <c r="AS126" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_TOXO_ANNUAL</t>
+          <t>SER_LU_ECDC_CRYP_ANNUAL</t>
         </is>
       </c>
       <c r="AT126" t="n">
@@ -18731,22 +18731,22 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>D091</t>
+          <t>D099</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Botulism</t>
+          <t>Giardiasis</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>肉毒杆菌中毒</t>
+          <t>贾第虫病</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Parasitic</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -18760,17 +18760,17 @@
         </is>
       </c>
       <c r="N127" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O127" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R127" t="n">
-        <v>0</v>
+        <v>0.4014560812065361</v>
       </c>
       <c r="U127" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_BOTU_ANNUAL</t>
+          <t>SER_LU_ECDC_GIAR_ANNUAL</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -18790,7 +18790,7 @@
       </c>
       <c r="AS127" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_BOTU_ANNUAL</t>
+          <t>SER_LU_ECDC_GIAR_ANNUAL</t>
         </is>
       </c>
       <c r="AT127" t="n">
@@ -18875,17 +18875,17 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>D092</t>
+          <t>D100</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Campylobacteriosis</t>
+          <t>Haemophilus influenzae</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>弯曲杆菌病</t>
+          <t>流感嗜血杆菌</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -18904,17 +18904,17 @@
         </is>
       </c>
       <c r="N128" t="n">
-        <v>523</v>
+        <v>0</v>
       </c>
       <c r="O128" t="n">
-        <v>523</v>
+        <v>0</v>
       </c>
       <c r="R128" t="n">
-        <v>104.9807652355092</v>
+        <v>0</v>
       </c>
       <c r="U128" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_CAMP_ANNUAL</t>
+          <t>SER_LU_ECDC_HAEINF_ANNUAL</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AS128" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_CAMP_ANNUAL</t>
+          <t>SER_LU_ECDC_HAEINF_ANNUAL</t>
         </is>
       </c>
       <c r="AT128" t="n">
@@ -19019,22 +19019,22 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>D096</t>
+          <t>D102</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Cryptosporidiosis</t>
+          <t>Hantavirus infection</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>隐孢子虫病</t>
+          <t>汉坦病毒感染</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>Parasitic</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -19048,17 +19048,17 @@
         </is>
       </c>
       <c r="N129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R129" t="n">
-        <v>0</v>
+        <v>0.200728040603268</v>
       </c>
       <c r="U129" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_CRYP_ANNUAL</t>
+          <t>SER_LU_ECDC_HANTA_ANNUAL</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -19078,7 +19078,7 @@
       </c>
       <c r="AS129" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_CRYP_ANNUAL</t>
+          <t>SER_LU_ECDC_HANTA_ANNUAL</t>
         </is>
       </c>
       <c r="AT129" t="n">
@@ -19163,22 +19163,22 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>D099</t>
+          <t>D105</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Giardiasis</t>
+          <t>Shigellosis</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>贾第虫病</t>
+          <t>志贺菌病</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>Parasitic</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -19192,17 +19192,17 @@
         </is>
       </c>
       <c r="N130" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="O130" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="R130" t="n">
-        <v>0.4014560812065361</v>
+        <v>3.010920609049021</v>
       </c>
       <c r="U130" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_GIAR_ANNUAL</t>
+          <t>SER_LU_ECDC_SHIG_ANNUAL</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -19222,7 +19222,7 @@
       </c>
       <c r="AS130" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_GIAR_ANNUAL</t>
+          <t>SER_LU_ECDC_SHIG_ANNUAL</t>
         </is>
       </c>
       <c r="AT130" t="n">
@@ -19307,17 +19307,17 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>D100</t>
+          <t>D107</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Haemophilus influenzae</t>
+          <t>Legionellosis</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>流感嗜血杆菌</t>
+          <t>军团菌病</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
@@ -19336,17 +19336,17 @@
         </is>
       </c>
       <c r="N131" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O131" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R131" t="n">
-        <v>0</v>
+        <v>1.00364020301634</v>
       </c>
       <c r="U131" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_HAEINF_ANNUAL</t>
+          <t>SER_LU_ECDC_LEGI_ANNUAL</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -19366,7 +19366,7 @@
       </c>
       <c r="AS131" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_HAEINF_ANNUAL</t>
+          <t>SER_LU_ECDC_LEGI_ANNUAL</t>
         </is>
       </c>
       <c r="AT131" t="n">
@@ -19451,22 +19451,22 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>D102</t>
+          <t>D108</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Hantavirus infection</t>
+          <t>Listeriosis</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>汉坦病毒感染</t>
+          <t>李斯特菌病</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -19480,17 +19480,17 @@
         </is>
       </c>
       <c r="N132" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O132" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R132" t="n">
-        <v>0.200728040603268</v>
+        <v>0.6021841218098042</v>
       </c>
       <c r="U132" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_HANTA_ANNUAL</t>
+          <t>SER_LU_ECDC_LIST_ANNUAL</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -19510,7 +19510,7 @@
       </c>
       <c r="AS132" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_HANTA_ANNUAL</t>
+          <t>SER_LU_ECDC_LIST_ANNUAL</t>
         </is>
       </c>
       <c r="AT132" t="n">
@@ -19595,17 +19595,17 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>D105</t>
+          <t>D110</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Shigellosis</t>
+          <t>Meningococcal disease</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>志贺菌病</t>
+          <t>脑膜炎球菌病</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
@@ -19624,17 +19624,17 @@
         </is>
       </c>
       <c r="N133" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="O133" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="R133" t="n">
-        <v>3.010920609049021</v>
+        <v>0.6021841218098042</v>
       </c>
       <c r="U133" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_SHIG_ANNUAL</t>
+          <t>SER_LU_ECDC_MENI_ANNUAL</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -19654,7 +19654,7 @@
       </c>
       <c r="AS133" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_SHIG_ANNUAL</t>
+          <t>SER_LU_ECDC_MENI_ANNUAL</t>
         </is>
       </c>
       <c r="AT133" t="n">
@@ -19739,17 +19739,17 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>D107</t>
+          <t>D113</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Legionellosis</t>
+          <t>Q fever</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>军团菌病</t>
+          <t>Q热</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
@@ -19768,17 +19768,17 @@
         </is>
       </c>
       <c r="N134" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O134" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R134" t="n">
-        <v>1.00364020301634</v>
+        <v>0</v>
       </c>
       <c r="U134" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_LEGI_ANNUAL</t>
+          <t>SER_LU_ECDC_QFEV_ANNUAL</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -19798,7 +19798,7 @@
       </c>
       <c r="AS134" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_LEGI_ANNUAL</t>
+          <t>SER_LU_ECDC_QFEV_ANNUAL</t>
         </is>
       </c>
       <c r="AT134" t="n">
@@ -19883,17 +19883,17 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>D108</t>
+          <t>D114</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Listeriosis</t>
+          <t>Salmonellosis</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>李斯特菌病</t>
+          <t>沙门氏菌病</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
@@ -19912,17 +19912,17 @@
         </is>
       </c>
       <c r="N135" t="n">
-        <v>3</v>
+        <v>162</v>
       </c>
       <c r="O135" t="n">
-        <v>3</v>
+        <v>162</v>
       </c>
       <c r="R135" t="n">
-        <v>0.6021841218098042</v>
+        <v>32.51794257772943</v>
       </c>
       <c r="U135" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_LIST_ANNUAL</t>
+          <t>SER_LU_ECDC_SALM_ANNUAL</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -19942,7 +19942,7 @@
       </c>
       <c r="AS135" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_LIST_ANNUAL</t>
+          <t>SER_LU_ECDC_SALM_ANNUAL</t>
         </is>
       </c>
       <c r="AT135" t="n">
@@ -20027,17 +20027,17 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>D110</t>
+          <t>D115</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Meningococcal disease</t>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>脑膜炎球菌病</t>
+          <t>产志贺毒素大肠杆菌感染</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
@@ -20056,17 +20056,17 @@
         </is>
       </c>
       <c r="N136" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O136" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R136" t="n">
-        <v>0.6021841218098042</v>
+        <v>1.00364020301634</v>
       </c>
       <c r="U136" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_MENI_ANNUAL</t>
+          <t>SER_LU_ECDC_STEC_ANNUAL</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -20086,7 +20086,7 @@
       </c>
       <c r="AS136" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_MENI_ANNUAL</t>
+          <t>SER_LU_ECDC_STEC_ANNUAL</t>
         </is>
       </c>
       <c r="AT136" t="n">
@@ -20171,17 +20171,17 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>D113</t>
+          <t>D120</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Q fever</t>
+          <t>Tetanus</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>Q热</t>
+          <t>破伤风</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
@@ -20210,7 +20210,7 @@
       </c>
       <c r="U137" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_QFEV_ANNUAL</t>
+          <t>SER_LU_ECDC_TETA_ANNUAL</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -20230,7 +20230,7 @@
       </c>
       <c r="AS137" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_QFEV_ANNUAL</t>
+          <t>SER_LU_ECDC_TETA_ANNUAL</t>
         </is>
       </c>
       <c r="AT137" t="n">
@@ -20315,22 +20315,22 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>D114</t>
+          <t>D122</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Salmonellosis</t>
+          <t>Trichinellosis</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>沙门氏菌病</t>
+          <t>旋毛虫病</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Parasitic</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -20344,17 +20344,17 @@
         </is>
       </c>
       <c r="N138" t="n">
-        <v>162</v>
+        <v>0</v>
       </c>
       <c r="O138" t="n">
-        <v>162</v>
+        <v>0</v>
       </c>
       <c r="R138" t="n">
-        <v>32.51794257772943</v>
+        <v>0</v>
       </c>
       <c r="U138" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_SALM_ANNUAL</t>
+          <t>SER_LU_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -20374,7 +20374,7 @@
       </c>
       <c r="AS138" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_SALM_ANNUAL</t>
+          <t>SER_LU_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AT138" t="n">
@@ -20459,17 +20459,17 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>D115</t>
+          <t>D123</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Shiga toxin-producing Escherichia coli infection</t>
+          <t>Tularemia</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>产志贺毒素大肠杆菌感染</t>
+          <t>土拉菌病</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
@@ -20488,17 +20488,17 @@
         </is>
       </c>
       <c r="N139" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O139" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R139" t="n">
-        <v>1.00364020301634</v>
+        <v>0</v>
       </c>
       <c r="U139" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_STEC_ANNUAL</t>
+          <t>SER_LU_ECDC_TULA_ANNUAL</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -20518,7 +20518,7 @@
       </c>
       <c r="AS139" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_STEC_ANNUAL</t>
+          <t>SER_LU_ECDC_TULA_ANNUAL</t>
         </is>
       </c>
       <c r="AT139" t="n">
@@ -20603,22 +20603,22 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>D120</t>
+          <t>D127</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Tetanus</t>
+          <t>Viral hemorrhagic fevers</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>破伤风</t>
+          <t>病毒性出血热</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
@@ -20642,7 +20642,7 @@
       </c>
       <c r="U140" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_TETA_ANNUAL</t>
+          <t>SER_LU_ECDC_VHFOTH_ANNUAL</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -20662,7 +20662,7 @@
       </c>
       <c r="AS140" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_TETA_ANNUAL</t>
+          <t>SER_LU_ECDC_VHFOTH_ANNUAL</t>
         </is>
       </c>
       <c r="AT140" t="n">
@@ -20747,22 +20747,22 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>D122</t>
+          <t>D128</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Trichinellosis</t>
+          <t>West Nile virus</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>旋毛虫病</t>
+          <t>西尼罗病毒</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>Parasitic</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
@@ -20786,7 +20786,7 @@
       </c>
       <c r="U141" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_TRIC_ANNUAL</t>
+          <t>SER_LU_ECDC_WNF_ANNUAL</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -20806,7 +20806,7 @@
       </c>
       <c r="AS141" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_TRIC_ANNUAL</t>
+          <t>SER_LU_ECDC_WNF_ANNUAL</t>
         </is>
       </c>
       <c r="AT141" t="n">
@@ -20891,22 +20891,22 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>D123</t>
+          <t>D144</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Tularemia</t>
+          <t>Creutzfeldt-Jakob disease</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>土拉菌病</t>
+          <t>克雅氏病</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Prion</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -20930,7 +20930,7 @@
       </c>
       <c r="U142" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_TULA_ANNUAL</t>
+          <t>SER_LU_ECDC_VCJD_ANNUAL</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -20950,7 +20950,7 @@
       </c>
       <c r="AS142" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_TULA_ANNUAL</t>
+          <t>SER_LU_ECDC_VCJD_ANNUAL</t>
         </is>
       </c>
       <c r="AT142" t="n">
@@ -21035,22 +21035,22 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>D127</t>
+          <t>D155</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Viral hemorrhagic fevers</t>
+          <t>Yersiniosis</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>病毒性出血热</t>
+          <t>耶尔森菌病</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
@@ -21064,17 +21064,17 @@
         </is>
       </c>
       <c r="N143" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="O143" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="R143" t="n">
-        <v>0</v>
+        <v>4.616744933875165</v>
       </c>
       <c r="U143" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_VHFOTH_ANNUAL</t>
+          <t>SER_LU_ECDC_YERS_ANNUAL</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -21094,7 +21094,7 @@
       </c>
       <c r="AS143" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_VHFOTH_ANNUAL</t>
+          <t>SER_LU_ECDC_YERS_ANNUAL</t>
         </is>
       </c>
       <c r="AT143" t="n">
@@ -21179,17 +21179,17 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>D128</t>
+          <t>D162</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>West Nile virus</t>
+          <t>HIV infection</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>西尼罗病毒</t>
+          <t>人类免疫缺乏病毒感染</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
@@ -21208,17 +21208,17 @@
         </is>
       </c>
       <c r="N144" t="n">
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="O144" t="n">
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="R144" t="n">
-        <v>0</v>
+        <v>27.90119764385426</v>
       </c>
       <c r="U144" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_WNF_ANNUAL</t>
+          <t>SER_LU_ECDC_HIV_INFECTION_ANNUAL</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -21238,7 +21238,7 @@
       </c>
       <c r="AS144" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_WNF_ANNUAL</t>
+          <t>SER_LU_ECDC_HIV_INFECTION_ANNUAL</t>
         </is>
       </c>
       <c r="AT144" t="n">
@@ -21323,22 +21323,22 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>D144</t>
+          <t>D167</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>Creutzfeldt-Jakob disease</t>
+          <t>Congenital syphilis</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>克雅氏病</t>
+          <t>先天性梅毒</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>Prion</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
@@ -21362,7 +21362,7 @@
       </c>
       <c r="U145" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_VCJD_ANNUAL</t>
+          <t>SER_LU_ECDC_CONSYPH_ANNUAL</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -21382,7 +21382,7 @@
       </c>
       <c r="AS145" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_VCJD_ANNUAL</t>
+          <t>SER_LU_ECDC_CONSYPH_ANNUAL</t>
         </is>
       </c>
       <c r="AT145" t="n">
@@ -21467,22 +21467,22 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>D155</t>
+          <t>D173</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Yersiniosis</t>
+          <t>Rift Valley fever</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>耶尔森菌病</t>
+          <t>裂谷热</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
@@ -21496,17 +21496,17 @@
         </is>
       </c>
       <c r="N146" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="O146" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="R146" t="n">
-        <v>4.616744933875165</v>
+        <v>0</v>
       </c>
       <c r="U146" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_YERS_ANNUAL</t>
+          <t>SER_LU_ECDC_RIFT_ANNUAL</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -21526,7 +21526,7 @@
       </c>
       <c r="AS146" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_YERS_ANNUAL</t>
+          <t>SER_LU_ECDC_RIFT_ANNUAL</t>
         </is>
       </c>
       <c r="AT146" t="n">
@@ -21611,17 +21611,17 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>D162</t>
+          <t>D203</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>HIV infection</t>
+          <t>Crimean-Congo hemorrhagic fever</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>人类免疫缺乏病毒感染</t>
+          <t>克里米亚-刚果出血热</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
@@ -21640,17 +21640,17 @@
         </is>
       </c>
       <c r="N147" t="n">
-        <v>139</v>
+        <v>0</v>
       </c>
       <c r="O147" t="n">
-        <v>139</v>
+        <v>0</v>
       </c>
       <c r="R147" t="n">
-        <v>27.90119764385426</v>
+        <v>0</v>
       </c>
       <c r="U147" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_HIV_INFECTION_ANNUAL</t>
+          <t>SER_LU_ECDC_CCHF_ANNUAL</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -21670,7 +21670,7 @@
       </c>
       <c r="AS147" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_HIV_INFECTION_ANNUAL</t>
+          <t>SER_LU_ECDC_CCHF_ANNUAL</t>
         </is>
       </c>
       <c r="AT147" t="n">
@@ -21755,17 +21755,17 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>D167</t>
+          <t>D242</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>Congenital syphilis</t>
+          <t>Lymphogranuloma venereum</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>先天性梅毒</t>
+          <t>性病性淋巴肉芽肿</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
@@ -21794,7 +21794,7 @@
       </c>
       <c r="U148" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_CONSYPH_ANNUAL</t>
+          <t>SER_LU_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -21814,7 +21814,7 @@
       </c>
       <c r="AS148" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_CONSYPH_ANNUAL</t>
+          <t>SER_LU_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT148" t="n">
@@ -21856,438 +21856,6 @@
         </is>
       </c>
       <c r="BC148" t="inlineStr">
-        <is>
-          <t>official_ecdc_rest_aggregate</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>country</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>lu</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>lu</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>Luxembourg</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>LU</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>Luxembourg</t>
-        </is>
-      </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>D173</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>Rift Valley fever</t>
-        </is>
-      </c>
-      <c r="J149" t="inlineStr">
-        <is>
-          <t>裂谷热</t>
-        </is>
-      </c>
-      <c r="K149" t="inlineStr">
-        <is>
-          <t>Viral</t>
-        </is>
-      </c>
-      <c r="L149" t="inlineStr">
-        <is>
-          <t>2009-01-01</t>
-        </is>
-      </c>
-      <c r="M149" t="inlineStr">
-        <is>
-          <t>2009-01</t>
-        </is>
-      </c>
-      <c r="N149" t="n">
-        <v>0</v>
-      </c>
-      <c r="O149" t="n">
-        <v>0</v>
-      </c>
-      <c r="R149" t="n">
-        <v>0</v>
-      </c>
-      <c r="U149" t="inlineStr">
-        <is>
-          <t>SER_LU_ECDC_RIFT_ANNUAL</t>
-        </is>
-      </c>
-      <c r="AA149" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AO149" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP149" t="inlineStr">
-        <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS149" t="inlineStr">
-        <is>
-          <t>SER_LU_ECDC_RIFT_ANNUAL</t>
-        </is>
-      </c>
-      <c r="AT149" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV149" t="inlineStr">
-        <is>
-          <t>ecdc_atlas_annual</t>
-        </is>
-      </c>
-      <c r="AW149" t="inlineStr">
-        <is>
-          <t>ECDC Surveillance Atlas — Luxembourg Annual Baseline</t>
-        </is>
-      </c>
-      <c r="AX149" t="inlineStr">
-        <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
-        </is>
-      </c>
-      <c r="AY149" t="inlineStr">
-        <is>
-          <t>official_ecdc_rest_aggregate</t>
-        </is>
-      </c>
-      <c r="AZ149" t="inlineStr">
-        <is>
-          <t>ecdc_atlas_annual</t>
-        </is>
-      </c>
-      <c r="BA149" t="inlineStr">
-        <is>
-          <t>ECDC Surveillance Atlas — Luxembourg Annual Baseline</t>
-        </is>
-      </c>
-      <c r="BB149" t="inlineStr">
-        <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
-        </is>
-      </c>
-      <c r="BC149" t="inlineStr">
-        <is>
-          <t>official_ecdc_rest_aggregate</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>country</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>lu</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>lu</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>Luxembourg</t>
-        </is>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>LU</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>Luxembourg</t>
-        </is>
-      </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>D203</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>Crimean-Congo hemorrhagic fever</t>
-        </is>
-      </c>
-      <c r="J150" t="inlineStr">
-        <is>
-          <t>克里米亚-刚果出血热</t>
-        </is>
-      </c>
-      <c r="K150" t="inlineStr">
-        <is>
-          <t>Viral</t>
-        </is>
-      </c>
-      <c r="L150" t="inlineStr">
-        <is>
-          <t>2009-01-01</t>
-        </is>
-      </c>
-      <c r="M150" t="inlineStr">
-        <is>
-          <t>2009-01</t>
-        </is>
-      </c>
-      <c r="N150" t="n">
-        <v>0</v>
-      </c>
-      <c r="O150" t="n">
-        <v>0</v>
-      </c>
-      <c r="R150" t="n">
-        <v>0</v>
-      </c>
-      <c r="U150" t="inlineStr">
-        <is>
-          <t>SER_LU_ECDC_CCHF_ANNUAL</t>
-        </is>
-      </c>
-      <c r="AA150" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AO150" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP150" t="inlineStr">
-        <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS150" t="inlineStr">
-        <is>
-          <t>SER_LU_ECDC_CCHF_ANNUAL</t>
-        </is>
-      </c>
-      <c r="AT150" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV150" t="inlineStr">
-        <is>
-          <t>ecdc_atlas_annual</t>
-        </is>
-      </c>
-      <c r="AW150" t="inlineStr">
-        <is>
-          <t>ECDC Surveillance Atlas — Luxembourg Annual Baseline</t>
-        </is>
-      </c>
-      <c r="AX150" t="inlineStr">
-        <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
-        </is>
-      </c>
-      <c r="AY150" t="inlineStr">
-        <is>
-          <t>official_ecdc_rest_aggregate</t>
-        </is>
-      </c>
-      <c r="AZ150" t="inlineStr">
-        <is>
-          <t>ecdc_atlas_annual</t>
-        </is>
-      </c>
-      <c r="BA150" t="inlineStr">
-        <is>
-          <t>ECDC Surveillance Atlas — Luxembourg Annual Baseline</t>
-        </is>
-      </c>
-      <c r="BB150" t="inlineStr">
-        <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
-        </is>
-      </c>
-      <c r="BC150" t="inlineStr">
-        <is>
-          <t>official_ecdc_rest_aggregate</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>country</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>lu</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>lu</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>Luxembourg</t>
-        </is>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>LU</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>Luxembourg</t>
-        </is>
-      </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>D242</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t>Lymphogranuloma venereum</t>
-        </is>
-      </c>
-      <c r="J151" t="inlineStr">
-        <is>
-          <t>性病性淋巴肉芽肿</t>
-        </is>
-      </c>
-      <c r="K151" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L151" t="inlineStr">
-        <is>
-          <t>2009-01-01</t>
-        </is>
-      </c>
-      <c r="M151" t="inlineStr">
-        <is>
-          <t>2009-01</t>
-        </is>
-      </c>
-      <c r="N151" t="n">
-        <v>0</v>
-      </c>
-      <c r="O151" t="n">
-        <v>0</v>
-      </c>
-      <c r="R151" t="n">
-        <v>0</v>
-      </c>
-      <c r="U151" t="inlineStr">
-        <is>
-          <t>SER_LU_ECDC_LGV_ANNUAL</t>
-        </is>
-      </c>
-      <c r="AA151" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AO151" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP151" t="inlineStr">
-        <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS151" t="inlineStr">
-        <is>
-          <t>SER_LU_ECDC_LGV_ANNUAL</t>
-        </is>
-      </c>
-      <c r="AT151" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV151" t="inlineStr">
-        <is>
-          <t>ecdc_atlas_annual</t>
-        </is>
-      </c>
-      <c r="AW151" t="inlineStr">
-        <is>
-          <t>ECDC Surveillance Atlas — Luxembourg Annual Baseline</t>
-        </is>
-      </c>
-      <c r="AX151" t="inlineStr">
-        <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
-        </is>
-      </c>
-      <c r="AY151" t="inlineStr">
-        <is>
-          <t>official_ecdc_rest_aggregate</t>
-        </is>
-      </c>
-      <c r="AZ151" t="inlineStr">
-        <is>
-          <t>ecdc_atlas_annual</t>
-        </is>
-      </c>
-      <c r="BA151" t="inlineStr">
-        <is>
-          <t>ECDC Surveillance Atlas — Luxembourg Annual Baseline</t>
-        </is>
-      </c>
-      <c r="BB151" t="inlineStr">
-        <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
-        </is>
-      </c>
-      <c r="BC151" t="inlineStr">
         <is>
           <t>official_ecdc_rest_aggregate</t>
         </is>
@@ -22409,7 +21977,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="10">
@@ -22419,7 +21987,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="11">

--- a/countries/lu/2005-2009.xlsx
+++ b/countries/lu/2005-2009.xlsx
@@ -6779,22 +6779,22 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>D045</t>
+          <t>D040</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Echinococcosis</t>
+          <t>Rubella</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>包虫病</t>
+          <t>风疹</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Parasitic</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -6818,7 +6818,7 @@
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_ECHI_ANNUAL</t>
+          <t>SER_LU_ECDC_RUBE_ANNUAL</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6838,7 +6838,7 @@
       </c>
       <c r="AS44" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_ECHI_ANNUAL</t>
+          <t>SER_LU_ECDC_RUBE_ANNUAL</t>
         </is>
       </c>
       <c r="AT44" t="n">
@@ -6923,22 +6923,22 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>D059</t>
+          <t>D045</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Yellow fever</t>
+          <t>Echinococcosis</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>黄热病</t>
+          <t>包虫病</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Parasitic</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -6962,7 +6962,7 @@
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_YELF_ANNUAL</t>
+          <t>SER_LU_ECDC_ECHI_ANNUAL</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6982,7 +6982,7 @@
       </c>
       <c r="AS45" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_YELF_ANNUAL</t>
+          <t>SER_LU_ECDC_ECHI_ANNUAL</t>
         </is>
       </c>
       <c r="AT45" t="n">
@@ -7067,22 +7067,22 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>D085</t>
+          <t>D059</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Toxoplasmosis</t>
+          <t>Yellow fever</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>弓形体病</t>
+          <t>黄热病</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Parasitic</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -7106,7 +7106,7 @@
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_TOXO_ANNUAL</t>
+          <t>SER_LU_ECDC_YELF_ANNUAL</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -7126,7 +7126,7 @@
       </c>
       <c r="AS46" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_TOXO_ANNUAL</t>
+          <t>SER_LU_ECDC_YELF_ANNUAL</t>
         </is>
       </c>
       <c r="AT46" t="n">
@@ -7211,22 +7211,22 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>D091</t>
+          <t>D085</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Botulism</t>
+          <t>Toxoplasmosis</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>肉毒杆菌中毒</t>
+          <t>弓形体病</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Parasitic</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -7250,7 +7250,7 @@
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_BOTU_ANNUAL</t>
+          <t>SER_LU_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -7270,7 +7270,7 @@
       </c>
       <c r="AS47" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_BOTU_ANNUAL</t>
+          <t>SER_LU_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT47" t="n">
@@ -7355,17 +7355,17 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>D092</t>
+          <t>D091</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Campylobacteriosis</t>
+          <t>Botulism</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>弯曲杆菌病</t>
+          <t>肉毒杆菌中毒</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -7384,17 +7384,17 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>366</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>366</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>76.20713348741333</v>
+        <v>0</v>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_CAMP_ANNUAL</t>
+          <t>SER_LU_ECDC_BOTU_ANNUAL</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -7414,7 +7414,7 @@
       </c>
       <c r="AS48" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_CAMP_ANNUAL</t>
+          <t>SER_LU_ECDC_BOTU_ANNUAL</t>
         </is>
       </c>
       <c r="AT48" t="n">
@@ -7499,22 +7499,22 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>D096</t>
+          <t>D092</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Cryptosporidiosis</t>
+          <t>Campylobacteriosis</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>隐孢子虫病</t>
+          <t>弯曲杆菌病</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Parasitic</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -7528,17 +7528,17 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>366</v>
       </c>
       <c r="O49" t="n">
-        <v>0</v>
+        <v>366</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>76.20713348741333</v>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_CRYP_ANNUAL</t>
+          <t>SER_LU_ECDC_CAMP_ANNUAL</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -7558,7 +7558,7 @@
       </c>
       <c r="AS49" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_CRYP_ANNUAL</t>
+          <t>SER_LU_ECDC_CAMP_ANNUAL</t>
         </is>
       </c>
       <c r="AT49" t="n">
@@ -7643,17 +7643,17 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>D099</t>
+          <t>D096</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Giardiasis</t>
+          <t>Cryptosporidiosis</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>贾第虫病</t>
+          <t>隐孢子虫病</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -7682,7 +7682,7 @@
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_GIAR_ANNUAL</t>
+          <t>SER_LU_ECDC_CRYP_ANNUAL</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -7702,7 +7702,7 @@
       </c>
       <c r="AS50" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_GIAR_ANNUAL</t>
+          <t>SER_LU_ECDC_CRYP_ANNUAL</t>
         </is>
       </c>
       <c r="AT50" t="n">
@@ -7787,22 +7787,22 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>D100</t>
+          <t>D099</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Haemophilus influenzae</t>
+          <t>Giardiasis</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>流感嗜血杆菌</t>
+          <t>贾第虫病</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Parasitic</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -7816,17 +7816,17 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>0.2082162117142441</v>
+        <v>0</v>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_HAEINF_ANNUAL</t>
+          <t>SER_LU_ECDC_GIAR_ANNUAL</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="AS51" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_HAEINF_ANNUAL</t>
+          <t>SER_LU_ECDC_GIAR_ANNUAL</t>
         </is>
       </c>
       <c r="AT51" t="n">
@@ -7931,17 +7931,17 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>D105</t>
+          <t>D100</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Shigellosis</t>
+          <t>Haemophilus influenzae</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>志贺菌病</t>
+          <t>流感嗜血杆菌</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -7960,17 +7960,17 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="O52" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="R52" t="n">
-        <v>2.08216211714244</v>
+        <v>0.2082162117142441</v>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_SHIG_ANNUAL</t>
+          <t>SER_LU_ECDC_HAEINF_ANNUAL</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7990,7 +7990,7 @@
       </c>
       <c r="AS52" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_SHIG_ANNUAL</t>
+          <t>SER_LU_ECDC_HAEINF_ANNUAL</t>
         </is>
       </c>
       <c r="AT52" t="n">
@@ -8075,17 +8075,17 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>D107</t>
+          <t>D105</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Legionellosis</t>
+          <t>Shigellosis</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>军团菌病</t>
+          <t>志贺菌病</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -8104,17 +8104,17 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="O53" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="R53" t="n">
-        <v>1.04108105857122</v>
+        <v>2.08216211714244</v>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_LEGI_ANNUAL</t>
+          <t>SER_LU_ECDC_SHIG_ANNUAL</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -8134,7 +8134,7 @@
       </c>
       <c r="AS53" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_LEGI_ANNUAL</t>
+          <t>SER_LU_ECDC_SHIG_ANNUAL</t>
         </is>
       </c>
       <c r="AT53" t="n">
@@ -8219,17 +8219,17 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>D108</t>
+          <t>D107</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Listeriosis</t>
+          <t>Legionellosis</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>李斯特菌病</t>
+          <t>军团菌病</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -8248,17 +8248,17 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O54" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R54" t="n">
-        <v>1.249297270285464</v>
+        <v>1.04108105857122</v>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_LIST_ANNUAL</t>
+          <t>SER_LU_ECDC_LEGI_ANNUAL</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -8278,7 +8278,7 @@
       </c>
       <c r="AS54" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_LIST_ANNUAL</t>
+          <t>SER_LU_ECDC_LEGI_ANNUAL</t>
         </is>
       </c>
       <c r="AT54" t="n">
@@ -8363,17 +8363,17 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>D110</t>
+          <t>D108</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Meningococcal disease</t>
+          <t>Listeriosis</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>脑膜炎球菌病</t>
+          <t>李斯特菌病</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -8392,17 +8392,17 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O55" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="R55" t="n">
-        <v>0.4164324234284881</v>
+        <v>1.249297270285464</v>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_MENI_ANNUAL</t>
+          <t>SER_LU_ECDC_LIST_ANNUAL</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -8422,7 +8422,7 @@
       </c>
       <c r="AS55" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_MENI_ANNUAL</t>
+          <t>SER_LU_ECDC_LIST_ANNUAL</t>
         </is>
       </c>
       <c r="AT55" t="n">
@@ -8507,17 +8507,17 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>D114</t>
+          <t>D110</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Salmonellosis</t>
+          <t>Meningococcal disease</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>沙门氏菌病</t>
+          <t>脑膜炎球菌病</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -8536,17 +8536,17 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>163</v>
+        <v>2</v>
       </c>
       <c r="O56" t="n">
-        <v>163</v>
+        <v>2</v>
       </c>
       <c r="R56" t="n">
-        <v>33.93924250942178</v>
+        <v>0.4164324234284881</v>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_SALM_ANNUAL</t>
+          <t>SER_LU_ECDC_MENI_ANNUAL</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -8566,7 +8566,7 @@
       </c>
       <c r="AS56" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_SALM_ANNUAL</t>
+          <t>SER_LU_ECDC_MENI_ANNUAL</t>
         </is>
       </c>
       <c r="AT56" t="n">
@@ -8651,17 +8651,17 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>D115</t>
+          <t>D114</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Shiga toxin-producing Escherichia coli infection</t>
+          <t>Salmonellosis</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>产志贺毒素大肠杆菌感染</t>
+          <t>沙门氏菌病</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -8680,17 +8680,17 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>1</v>
+        <v>163</v>
       </c>
       <c r="O57" t="n">
-        <v>1</v>
+        <v>163</v>
       </c>
       <c r="R57" t="n">
-        <v>0.2082162117142441</v>
+        <v>33.93924250942178</v>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_STEC_ANNUAL</t>
+          <t>SER_LU_ECDC_SALM_ANNUAL</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -8710,7 +8710,7 @@
       </c>
       <c r="AS57" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_STEC_ANNUAL</t>
+          <t>SER_LU_ECDC_SALM_ANNUAL</t>
         </is>
       </c>
       <c r="AT57" t="n">
@@ -8795,17 +8795,17 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>D120</t>
+          <t>D115</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Tetanus</t>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>破伤风</t>
+          <t>产志贺毒素大肠杆菌感染</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -8824,17 +8824,17 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>0.2082162117142441</v>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_TETA_ANNUAL</t>
+          <t>SER_LU_ECDC_STEC_ANNUAL</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AS58" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_TETA_ANNUAL</t>
+          <t>SER_LU_ECDC_STEC_ANNUAL</t>
         </is>
       </c>
       <c r="AT58" t="n">
@@ -8939,22 +8939,22 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>D122</t>
+          <t>D120</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Trichinellosis</t>
+          <t>Tetanus</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>旋毛虫病</t>
+          <t>破伤风</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Parasitic</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -8978,7 +8978,7 @@
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_TRIC_ANNUAL</t>
+          <t>SER_LU_ECDC_TETA_ANNUAL</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -8998,7 +8998,7 @@
       </c>
       <c r="AS59" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_TRIC_ANNUAL</t>
+          <t>SER_LU_ECDC_TETA_ANNUAL</t>
         </is>
       </c>
       <c r="AT59" t="n">
@@ -9083,22 +9083,22 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>D144</t>
+          <t>D122</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Creutzfeldt-Jakob disease</t>
+          <t>Trichinellosis</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>克雅氏病</t>
+          <t>旋毛虫病</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Prion</t>
+          <t>Parasitic</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -9122,7 +9122,7 @@
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_VCJD_ANNUAL</t>
+          <t>SER_LU_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -9142,7 +9142,7 @@
       </c>
       <c r="AS60" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_VCJD_ANNUAL</t>
+          <t>SER_LU_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AT60" t="n">
@@ -9227,22 +9227,22 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>D155</t>
+          <t>D144</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Yersiniosis</t>
+          <t>Creutzfeldt-Jakob disease</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>耶尔森菌病</t>
+          <t>克雅氏病</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Prion</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -9256,17 +9256,17 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>4.58075665771337</v>
+        <v>0</v>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_YERS_ANNUAL</t>
+          <t>SER_LU_ECDC_VCJD_ANNUAL</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -9286,7 +9286,7 @@
       </c>
       <c r="AS61" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_YERS_ANNUAL</t>
+          <t>SER_LU_ECDC_VCJD_ANNUAL</t>
         </is>
       </c>
       <c r="AT61" t="n">
@@ -9371,22 +9371,22 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>D162</t>
+          <t>D155</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>HIV infection</t>
+          <t>Yersiniosis</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>人类免疫缺乏病毒感染</t>
+          <t>耶尔森菌病</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -9400,17 +9400,17 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>100</v>
+        <v>22</v>
       </c>
       <c r="O62" t="n">
-        <v>100</v>
+        <v>22</v>
       </c>
       <c r="R62" t="n">
-        <v>20.82162117142441</v>
+        <v>4.58075665771337</v>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_HIV_INFECTION_ANNUAL</t>
+          <t>SER_LU_ECDC_YERS_ANNUAL</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -9430,7 +9430,7 @@
       </c>
       <c r="AS62" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_HIV_INFECTION_ANNUAL</t>
+          <t>SER_LU_ECDC_YERS_ANNUAL</t>
         </is>
       </c>
       <c r="AT62" t="n">
@@ -9515,46 +9515,46 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>D002</t>
+          <t>D162</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Cholera</t>
+          <t>HIV infection</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>霍乱</t>
+          <t>人类免疫缺乏病毒感染</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>2008-01-01</t>
+          <t>2007-01-01</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>2008-01</t>
+          <t>2007-01</t>
         </is>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O63" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>20.82162117142441</v>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_CHOL_ANNUAL</t>
+          <t>SER_LU_ECDC_HIV_INFECTION_ANNUAL</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -9574,7 +9574,7 @@
       </c>
       <c r="AS63" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_CHOL_ANNUAL</t>
+          <t>SER_LU_ECDC_HIV_INFECTION_ANNUAL</t>
         </is>
       </c>
       <c r="AT63" t="n">
@@ -9659,22 +9659,22 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>D005</t>
+          <t>D002</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>AIDS</t>
+          <t>Cholera</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>艾滋病</t>
+          <t>霍乱</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -9688,17 +9688,17 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>3.067544256994768</v>
+        <v>0</v>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_AIDS_ANNUAL</t>
+          <t>SER_LU_ECDC_CHOL_ANNUAL</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -9718,7 +9718,7 @@
       </c>
       <c r="AS64" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_AIDS_ANNUAL</t>
+          <t>SER_LU_ECDC_CHOL_ANNUAL</t>
         </is>
       </c>
       <c r="AT64" t="n">
@@ -9803,17 +9803,17 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>D007</t>
+          <t>D005</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Hepatitis A</t>
+          <t>AIDS</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>甲型肝炎</t>
+          <t>艾滋病</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -9832,17 +9832,17 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="O65" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="R65" t="n">
-        <v>0.6135088513989535</v>
+        <v>3.067544256994768</v>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_HEPA_ANNUAL</t>
+          <t>SER_LU_ECDC_AIDS_ANNUAL</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -9862,7 +9862,7 @@
       </c>
       <c r="AS65" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_HEPA_ANNUAL</t>
+          <t>SER_LU_ECDC_AIDS_ANNUAL</t>
         </is>
       </c>
       <c r="AT65" t="n">
@@ -9947,17 +9947,17 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>D009</t>
+          <t>D007</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Hepatitis C</t>
+          <t>Hepatitis A</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>丙型肝炎</t>
+          <t>甲型肝炎</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -9976,17 +9976,17 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>58</v>
+        <v>3</v>
       </c>
       <c r="O66" t="n">
-        <v>58</v>
+        <v>3</v>
       </c>
       <c r="R66" t="n">
-        <v>11.86117112704644</v>
+        <v>0.6135088513989535</v>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_HEPC_ANNUAL</t>
+          <t>SER_LU_ECDC_HEPA_ANNUAL</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -10006,7 +10006,7 @@
       </c>
       <c r="AS66" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_HEPC_ANNUAL</t>
+          <t>SER_LU_ECDC_HEPA_ANNUAL</t>
         </is>
       </c>
       <c r="AT66" t="n">
@@ -10091,17 +10091,17 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>D017</t>
+          <t>D009</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Measles</t>
+          <t>Hepatitis C</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>麻疹</t>
+          <t>丙型肝炎</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -10120,17 +10120,17 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="O67" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>11.86117112704644</v>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_MEAS_ANNUAL</t>
+          <t>SER_LU_ECDC_HEPC_ANNUAL</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -10150,7 +10150,7 @@
       </c>
       <c r="AS67" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_MEAS_ANNUAL</t>
+          <t>SER_LU_ECDC_HEPC_ANNUAL</t>
         </is>
       </c>
       <c r="AT67" t="n">
@@ -10235,17 +10235,17 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>D019</t>
+          <t>D017</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Rabies</t>
+          <t>Measles</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>狂犬病</t>
+          <t>麻疹</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -10274,7 +10274,7 @@
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_RABI_ANNUAL</t>
+          <t>SER_LU_ECDC_MEAS_ANNUAL</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -10294,7 +10294,7 @@
       </c>
       <c r="AS68" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_RABI_ANNUAL</t>
+          <t>SER_LU_ECDC_MEAS_ANNUAL</t>
         </is>
       </c>
       <c r="AT68" t="n">
@@ -10379,17 +10379,17 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>D021</t>
+          <t>D019</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Dengue</t>
+          <t>Rabies</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>登革热</t>
+          <t>狂犬病</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -10418,7 +10418,7 @@
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_DENGUE_ANNUAL</t>
+          <t>SER_LU_ECDC_RABI_ANNUAL</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -10438,7 +10438,7 @@
       </c>
       <c r="AS69" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_DENGUE_ANNUAL</t>
+          <t>SER_LU_ECDC_RABI_ANNUAL</t>
         </is>
       </c>
       <c r="AT69" t="n">
@@ -10523,22 +10523,22 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>D023</t>
+          <t>D021</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Anthrax</t>
+          <t>Dengue</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>炭疽</t>
+          <t>登革热</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -10562,7 +10562,7 @@
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_ANTH_ANNUAL</t>
+          <t>SER_LU_ECDC_DENGUE_ANNUAL</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -10582,7 +10582,7 @@
       </c>
       <c r="AS70" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_ANTH_ANNUAL</t>
+          <t>SER_LU_ECDC_DENGUE_ANNUAL</t>
         </is>
       </c>
       <c r="AT70" t="n">
@@ -10667,17 +10667,17 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>D025</t>
+          <t>D023</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Tuberculosis</t>
+          <t>Anthrax</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>肺结核</t>
+          <t>炭疽</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -10696,17 +10696,17 @@
         </is>
       </c>
       <c r="N71" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="R71" t="n">
-        <v>5.7260826130569</v>
+        <v>0</v>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_TUBE_ANNUAL</t>
+          <t>SER_LU_ECDC_ANTH_ANNUAL</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -10726,7 +10726,7 @@
       </c>
       <c r="AS71" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_TUBE_ANNUAL</t>
+          <t>SER_LU_ECDC_ANTH_ANNUAL</t>
         </is>
       </c>
       <c r="AT71" t="n">
@@ -10811,17 +10811,17 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>D028</t>
+          <t>D025</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Pertussis</t>
+          <t>Tuberculosis</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>百日咳</t>
+          <t>肺结核</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -10840,17 +10840,17 @@
         </is>
       </c>
       <c r="N72" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="O72" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="R72" t="n">
-        <v>0.4090059009326357</v>
+        <v>5.7260826130569</v>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_PERT_ANNUAL</t>
+          <t>SER_LU_ECDC_TUBE_ANNUAL</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -10870,7 +10870,7 @@
       </c>
       <c r="AS72" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_PERT_ANNUAL</t>
+          <t>SER_LU_ECDC_TUBE_ANNUAL</t>
         </is>
       </c>
       <c r="AT72" t="n">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>D032</t>
+          <t>D028</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Brucellosis</t>
+          <t>Pertussis</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>布鲁氏菌病</t>
+          <t>百日咳</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -10984,17 +10984,17 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O73" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>0.4090059009326357</v>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_BRUC_ANNUAL</t>
+          <t>SER_LU_ECDC_PERT_ANNUAL</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -11014,7 +11014,7 @@
       </c>
       <c r="AS73" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_BRUC_ANNUAL</t>
+          <t>SER_LU_ECDC_PERT_ANNUAL</t>
         </is>
       </c>
       <c r="AT73" t="n">
@@ -11099,17 +11099,17 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>D033</t>
+          <t>D032</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Gonorrhea</t>
+          <t>Brucellosis</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>淋病</t>
+          <t>布鲁氏菌病</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -11128,17 +11128,17 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>3.681053108393721</v>
+        <v>0</v>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_GONO_ANNUAL</t>
+          <t>SER_LU_ECDC_BRUC_ANNUAL</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -11158,7 +11158,7 @@
       </c>
       <c r="AS74" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_GONO_ANNUAL</t>
+          <t>SER_LU_ECDC_BRUC_ANNUAL</t>
         </is>
       </c>
       <c r="AT74" t="n">
@@ -11243,17 +11243,17 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>D035</t>
+          <t>D033</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Leptospirosis</t>
+          <t>Gonorrhea</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>钩端螺旋体病</t>
+          <t>淋病</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -11272,17 +11272,17 @@
         </is>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="O75" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="R75" t="n">
-        <v>0</v>
+        <v>3.681053108393721</v>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_LEPT_ANNUAL</t>
+          <t>SER_LU_ECDC_GONO_ANNUAL</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -11302,7 +11302,7 @@
       </c>
       <c r="AS75" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_LEPT_ANNUAL</t>
+          <t>SER_LU_ECDC_GONO_ANNUAL</t>
         </is>
       </c>
       <c r="AT75" t="n">
@@ -11387,22 +11387,22 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>D037</t>
+          <t>D035</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Malaria</t>
+          <t>Leptospirosis</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>疟疾</t>
+          <t>钩端螺旋体病</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>Parasitic</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -11416,17 +11416,17 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O76" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R76" t="n">
-        <v>0.4090059009326357</v>
+        <v>0</v>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_MALA_ANNUAL</t>
+          <t>SER_LU_ECDC_LEPT_ANNUAL</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -11446,7 +11446,7 @@
       </c>
       <c r="AS76" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_MALA_ANNUAL</t>
+          <t>SER_LU_ECDC_LEPT_ANNUAL</t>
         </is>
       </c>
       <c r="AT76" t="n">
@@ -11531,22 +11531,22 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>D039</t>
+          <t>D037</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Mumps</t>
+          <t>Malaria</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>流行性腮腺炎</t>
+          <t>疟疾</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Parasitic</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -11560,17 +11560,17 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="O77" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="R77" t="n">
-        <v>5.7260826130569</v>
+        <v>0.4090059009326357</v>
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_MUMP_ANNUAL</t>
+          <t>SER_LU_ECDC_MALA_ANNUAL</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -11590,7 +11590,7 @@
       </c>
       <c r="AS77" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_MUMP_ANNUAL</t>
+          <t>SER_LU_ECDC_MALA_ANNUAL</t>
         </is>
       </c>
       <c r="AT77" t="n">
@@ -11675,22 +11675,22 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>D045</t>
+          <t>D039</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Echinococcosis</t>
+          <t>Mumps</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>包虫病</t>
+          <t>流行性腮腺炎</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>Parasitic</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -11704,17 +11704,17 @@
         </is>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="O78" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="R78" t="n">
-        <v>0</v>
+        <v>5.7260826130569</v>
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_ECHI_ANNUAL</t>
+          <t>SER_LU_ECDC_MUMP_ANNUAL</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -11734,7 +11734,7 @@
       </c>
       <c r="AS78" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_ECHI_ANNUAL</t>
+          <t>SER_LU_ECDC_MUMP_ANNUAL</t>
         </is>
       </c>
       <c r="AT78" t="n">
@@ -11819,17 +11819,17 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>D052</t>
+          <t>D040</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Chikungunya</t>
+          <t>Rubella</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>基孔肯雅热</t>
+          <t>风疹</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -11858,7 +11858,7 @@
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_CHIK_ANNUAL</t>
+          <t>SER_LU_ECDC_RUBE_ANNUAL</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -11878,7 +11878,7 @@
       </c>
       <c r="AS79" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_CHIK_ANNUAL</t>
+          <t>SER_LU_ECDC_RUBE_ANNUAL</t>
         </is>
       </c>
       <c r="AT79" t="n">
@@ -11963,22 +11963,22 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>D059</t>
+          <t>D045</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Yellow fever</t>
+          <t>Echinococcosis</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>黄热病</t>
+          <t>包虫病</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Parasitic</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -12002,7 +12002,7 @@
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_YELF_ANNUAL</t>
+          <t>SER_LU_ECDC_ECHI_ANNUAL</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -12022,7 +12022,7 @@
       </c>
       <c r="AS80" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_YELF_ANNUAL</t>
+          <t>SER_LU_ECDC_ECHI_ANNUAL</t>
         </is>
       </c>
       <c r="AT80" t="n">
@@ -12107,22 +12107,22 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>D085</t>
+          <t>D052</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Toxoplasmosis</t>
+          <t>Chikungunya</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>弓形体病</t>
+          <t>基孔肯雅热</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>Parasitic</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -12146,7 +12146,7 @@
       </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_TOXO_ANNUAL</t>
+          <t>SER_LU_ECDC_CHIK_ANNUAL</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="AS81" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_TOXO_ANNUAL</t>
+          <t>SER_LU_ECDC_CHIK_ANNUAL</t>
         </is>
       </c>
       <c r="AT81" t="n">
@@ -12251,22 +12251,22 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>D091</t>
+          <t>D059</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Botulism</t>
+          <t>Yellow fever</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>肉毒杆菌中毒</t>
+          <t>黄热病</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -12280,17 +12280,17 @@
         </is>
       </c>
       <c r="N82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R82" t="n">
-        <v>0.2045029504663179</v>
+        <v>0</v>
       </c>
       <c r="U82" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_BOTU_ANNUAL</t>
+          <t>SER_LU_ECDC_YELF_ANNUAL</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -12310,7 +12310,7 @@
       </c>
       <c r="AS82" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_BOTU_ANNUAL</t>
+          <t>SER_LU_ECDC_YELF_ANNUAL</t>
         </is>
       </c>
       <c r="AT82" t="n">
@@ -12395,22 +12395,22 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>D092</t>
+          <t>D085</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Campylobacteriosis</t>
+          <t>Toxoplasmosis</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>弯曲杆菌病</t>
+          <t>弓形体病</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Parasitic</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -12424,17 +12424,17 @@
         </is>
       </c>
       <c r="N83" t="n">
-        <v>467</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
-        <v>467</v>
+        <v>0</v>
       </c>
       <c r="R83" t="n">
-        <v>95.50287786777044</v>
+        <v>0</v>
       </c>
       <c r="U83" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_CAMP_ANNUAL</t>
+          <t>SER_LU_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -12454,7 +12454,7 @@
       </c>
       <c r="AS83" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_CAMP_ANNUAL</t>
+          <t>SER_LU_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT83" t="n">
@@ -12539,22 +12539,22 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>D096</t>
+          <t>D091</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Cryptosporidiosis</t>
+          <t>Botulism</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>隐孢子虫病</t>
+          <t>肉毒杆菌中毒</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>Parasitic</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -12568,17 +12568,17 @@
         </is>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R84" t="n">
-        <v>0</v>
+        <v>0.2045029504663179</v>
       </c>
       <c r="U84" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_CRYP_ANNUAL</t>
+          <t>SER_LU_ECDC_BOTU_ANNUAL</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -12598,7 +12598,7 @@
       </c>
       <c r="AS84" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_CRYP_ANNUAL</t>
+          <t>SER_LU_ECDC_BOTU_ANNUAL</t>
         </is>
       </c>
       <c r="AT84" t="n">
@@ -12683,22 +12683,22 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>D099</t>
+          <t>D092</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Giardiasis</t>
+          <t>Campylobacteriosis</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>贾第虫病</t>
+          <t>弯曲杆菌病</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>Parasitic</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -12712,17 +12712,17 @@
         </is>
       </c>
       <c r="N85" t="n">
-        <v>1</v>
+        <v>467</v>
       </c>
       <c r="O85" t="n">
-        <v>1</v>
+        <v>467</v>
       </c>
       <c r="R85" t="n">
-        <v>0.2045029504663179</v>
+        <v>95.50287786777044</v>
       </c>
       <c r="U85" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_GIAR_ANNUAL</t>
+          <t>SER_LU_ECDC_CAMP_ANNUAL</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -12742,7 +12742,7 @@
       </c>
       <c r="AS85" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_GIAR_ANNUAL</t>
+          <t>SER_LU_ECDC_CAMP_ANNUAL</t>
         </is>
       </c>
       <c r="AT85" t="n">
@@ -12827,22 +12827,22 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>D100</t>
+          <t>D096</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Haemophilus influenzae</t>
+          <t>Cryptosporidiosis</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>流感嗜血杆菌</t>
+          <t>隐孢子虫病</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Parasitic</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -12866,7 +12866,7 @@
       </c>
       <c r="U86" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_HAEINF_ANNUAL</t>
+          <t>SER_LU_ECDC_CRYP_ANNUAL</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -12886,7 +12886,7 @@
       </c>
       <c r="AS86" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_HAEINF_ANNUAL</t>
+          <t>SER_LU_ECDC_CRYP_ANNUAL</t>
         </is>
       </c>
       <c r="AT86" t="n">
@@ -12971,22 +12971,22 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>D102</t>
+          <t>D099</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Hantavirus infection</t>
+          <t>Giardiasis</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>汉坦病毒感染</t>
+          <t>贾第虫病</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Parasitic</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -13000,17 +13000,17 @@
         </is>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R87" t="n">
-        <v>0</v>
+        <v>0.2045029504663179</v>
       </c>
       <c r="U87" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_HANTA_ANNUAL</t>
+          <t>SER_LU_ECDC_GIAR_ANNUAL</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -13030,7 +13030,7 @@
       </c>
       <c r="AS87" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_HANTA_ANNUAL</t>
+          <t>SER_LU_ECDC_GIAR_ANNUAL</t>
         </is>
       </c>
       <c r="AT87" t="n">
@@ -13115,17 +13115,17 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>D105</t>
+          <t>D100</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Shigellosis</t>
+          <t>Haemophilus influenzae</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>志贺菌病</t>
+          <t>流感嗜血杆菌</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -13144,17 +13144,17 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="R88" t="n">
-        <v>3.681053108393721</v>
+        <v>0</v>
       </c>
       <c r="U88" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_SHIG_ANNUAL</t>
+          <t>SER_LU_ECDC_HAEINF_ANNUAL</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -13174,7 +13174,7 @@
       </c>
       <c r="AS88" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_SHIG_ANNUAL</t>
+          <t>SER_LU_ECDC_HAEINF_ANNUAL</t>
         </is>
       </c>
       <c r="AT88" t="n">
@@ -13259,22 +13259,22 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>D107</t>
+          <t>D102</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Legionellosis</t>
+          <t>Hantavirus infection</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>军团菌病</t>
+          <t>汉坦病毒感染</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -13288,17 +13288,17 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R89" t="n">
-        <v>1.022514752331589</v>
+        <v>0</v>
       </c>
       <c r="U89" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_LEGI_ANNUAL</t>
+          <t>SER_LU_ECDC_HANTA_ANNUAL</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -13318,7 +13318,7 @@
       </c>
       <c r="AS89" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_LEGI_ANNUAL</t>
+          <t>SER_LU_ECDC_HANTA_ANNUAL</t>
         </is>
       </c>
       <c r="AT89" t="n">
@@ -13403,17 +13403,17 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>D108</t>
+          <t>D105</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Listeriosis</t>
+          <t>Shigellosis</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>李斯特菌病</t>
+          <t>志贺菌病</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -13432,17 +13432,17 @@
         </is>
       </c>
       <c r="N90" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="O90" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="R90" t="n">
-        <v>0.2045029504663179</v>
+        <v>3.681053108393721</v>
       </c>
       <c r="U90" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_LIST_ANNUAL</t>
+          <t>SER_LU_ECDC_SHIG_ANNUAL</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -13462,7 +13462,7 @@
       </c>
       <c r="AS90" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_LIST_ANNUAL</t>
+          <t>SER_LU_ECDC_SHIG_ANNUAL</t>
         </is>
       </c>
       <c r="AT90" t="n">
@@ -13547,17 +13547,17 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>D110</t>
+          <t>D107</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Meningococcal disease</t>
+          <t>Legionellosis</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>脑膜炎球菌病</t>
+          <t>军团菌病</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -13576,17 +13576,17 @@
         </is>
       </c>
       <c r="N91" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O91" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R91" t="n">
-        <v>0.4090059009326357</v>
+        <v>1.022514752331589</v>
       </c>
       <c r="U91" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_MENI_ANNUAL</t>
+          <t>SER_LU_ECDC_LEGI_ANNUAL</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -13606,7 +13606,7 @@
       </c>
       <c r="AS91" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_MENI_ANNUAL</t>
+          <t>SER_LU_ECDC_LEGI_ANNUAL</t>
         </is>
       </c>
       <c r="AT91" t="n">
@@ -13691,17 +13691,17 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>D113</t>
+          <t>D108</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Q fever</t>
+          <t>Listeriosis</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Q热</t>
+          <t>李斯特菌病</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -13720,17 +13720,17 @@
         </is>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R92" t="n">
-        <v>0</v>
+        <v>0.2045029504663179</v>
       </c>
       <c r="U92" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_QFEV_ANNUAL</t>
+          <t>SER_LU_ECDC_LIST_ANNUAL</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -13750,7 +13750,7 @@
       </c>
       <c r="AS92" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_QFEV_ANNUAL</t>
+          <t>SER_LU_ECDC_LIST_ANNUAL</t>
         </is>
       </c>
       <c r="AT92" t="n">
@@ -13835,17 +13835,17 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>D114</t>
+          <t>D110</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Salmonellosis</t>
+          <t>Meningococcal disease</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>沙门氏菌病</t>
+          <t>脑膜炎球菌病</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -13864,17 +13864,17 @@
         </is>
       </c>
       <c r="N93" t="n">
-        <v>153</v>
+        <v>2</v>
       </c>
       <c r="O93" t="n">
-        <v>153</v>
+        <v>2</v>
       </c>
       <c r="R93" t="n">
-        <v>31.28895142134663</v>
+        <v>0.4090059009326357</v>
       </c>
       <c r="U93" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_SALM_ANNUAL</t>
+          <t>SER_LU_ECDC_MENI_ANNUAL</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AS93" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_SALM_ANNUAL</t>
+          <t>SER_LU_ECDC_MENI_ANNUAL</t>
         </is>
       </c>
       <c r="AT93" t="n">
@@ -13979,17 +13979,17 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>D115</t>
+          <t>D113</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Shiga toxin-producing Escherichia coli infection</t>
+          <t>Q fever</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>产志贺毒素大肠杆菌感染</t>
+          <t>Q热</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -14008,17 +14008,17 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O94" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R94" t="n">
-        <v>0.8180118018652714</v>
+        <v>0</v>
       </c>
       <c r="U94" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_STEC_ANNUAL</t>
+          <t>SER_LU_ECDC_QFEV_ANNUAL</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -14038,7 +14038,7 @@
       </c>
       <c r="AS94" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_STEC_ANNUAL</t>
+          <t>SER_LU_ECDC_QFEV_ANNUAL</t>
         </is>
       </c>
       <c r="AT94" t="n">
@@ -14123,17 +14123,17 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>D120</t>
+          <t>D114</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Tetanus</t>
+          <t>Salmonellosis</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>破伤风</t>
+          <t>沙门氏菌病</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -14152,17 +14152,17 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>153</v>
       </c>
       <c r="O95" t="n">
-        <v>0</v>
+        <v>153</v>
       </c>
       <c r="R95" t="n">
-        <v>0</v>
+        <v>31.28895142134663</v>
       </c>
       <c r="U95" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_TETA_ANNUAL</t>
+          <t>SER_LU_ECDC_SALM_ANNUAL</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -14182,7 +14182,7 @@
       </c>
       <c r="AS95" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_TETA_ANNUAL</t>
+          <t>SER_LU_ECDC_SALM_ANNUAL</t>
         </is>
       </c>
       <c r="AT95" t="n">
@@ -14267,22 +14267,22 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>D122</t>
+          <t>D115</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Trichinellosis</t>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>旋毛虫病</t>
+          <t>产志贺毒素大肠杆菌感染</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>Parasitic</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -14296,17 +14296,17 @@
         </is>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O96" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R96" t="n">
-        <v>0</v>
+        <v>0.8180118018652714</v>
       </c>
       <c r="U96" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_TRIC_ANNUAL</t>
+          <t>SER_LU_ECDC_STEC_ANNUAL</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -14326,7 +14326,7 @@
       </c>
       <c r="AS96" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_TRIC_ANNUAL</t>
+          <t>SER_LU_ECDC_STEC_ANNUAL</t>
         </is>
       </c>
       <c r="AT96" t="n">
@@ -14411,17 +14411,17 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>D123</t>
+          <t>D120</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Tularemia</t>
+          <t>Tetanus</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>土拉菌病</t>
+          <t>破伤风</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -14450,7 +14450,7 @@
       </c>
       <c r="U97" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_TULA_ANNUAL</t>
+          <t>SER_LU_ECDC_TETA_ANNUAL</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -14470,7 +14470,7 @@
       </c>
       <c r="AS97" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_TULA_ANNUAL</t>
+          <t>SER_LU_ECDC_TETA_ANNUAL</t>
         </is>
       </c>
       <c r="AT97" t="n">
@@ -14555,22 +14555,22 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>D127</t>
+          <t>D122</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Viral hemorrhagic fevers</t>
+          <t>Trichinellosis</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>病毒性出血热</t>
+          <t>旋毛虫病</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Parasitic</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -14594,7 +14594,7 @@
       </c>
       <c r="U98" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_VHFOTH_ANNUAL</t>
+          <t>SER_LU_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -14614,7 +14614,7 @@
       </c>
       <c r="AS98" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_VHFOTH_ANNUAL</t>
+          <t>SER_LU_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AT98" t="n">
@@ -14699,22 +14699,22 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>D128</t>
+          <t>D123</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>West Nile virus</t>
+          <t>Tularemia</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>西尼罗病毒</t>
+          <t>土拉菌病</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -14738,7 +14738,7 @@
       </c>
       <c r="U99" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_WNF_ANNUAL</t>
+          <t>SER_LU_ECDC_TULA_ANNUAL</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -14758,7 +14758,7 @@
       </c>
       <c r="AS99" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_WNF_ANNUAL</t>
+          <t>SER_LU_ECDC_TULA_ANNUAL</t>
         </is>
       </c>
       <c r="AT99" t="n">
@@ -14843,22 +14843,22 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>D144</t>
+          <t>D127</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Creutzfeldt-Jakob disease</t>
+          <t>Viral hemorrhagic fevers</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>克雅氏病</t>
+          <t>病毒性出血热</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>Prion</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -14882,7 +14882,7 @@
       </c>
       <c r="U100" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_VCJD_ANNUAL</t>
+          <t>SER_LU_ECDC_VHFOTH_ANNUAL</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -14902,7 +14902,7 @@
       </c>
       <c r="AS100" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_VCJD_ANNUAL</t>
+          <t>SER_LU_ECDC_VHFOTH_ANNUAL</t>
         </is>
       </c>
       <c r="AT100" t="n">
@@ -14987,22 +14987,22 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>D155</t>
+          <t>D128</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Yersiniosis</t>
+          <t>West Nile virus</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>耶尔森菌病</t>
+          <t>西尼罗病毒</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -15016,17 +15016,17 @@
         </is>
       </c>
       <c r="N101" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="O101" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="R101" t="n">
-        <v>3.476550157927404</v>
+        <v>0</v>
       </c>
       <c r="U101" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_YERS_ANNUAL</t>
+          <t>SER_LU_ECDC_WNF_ANNUAL</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -15046,7 +15046,7 @@
       </c>
       <c r="AS101" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_YERS_ANNUAL</t>
+          <t>SER_LU_ECDC_WNF_ANNUAL</t>
         </is>
       </c>
       <c r="AT101" t="n">
@@ -15131,22 +15131,22 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>D162</t>
+          <t>D144</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>HIV infection</t>
+          <t>Creutzfeldt-Jakob disease</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>人类免疫缺乏病毒感染</t>
+          <t>克雅氏病</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Prion</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -15160,17 +15160,17 @@
         </is>
       </c>
       <c r="N102" t="n">
-        <v>119</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
-        <v>119</v>
+        <v>0</v>
       </c>
       <c r="R102" t="n">
-        <v>24.33585110549182</v>
+        <v>0</v>
       </c>
       <c r="U102" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_HIV_INFECTION_ANNUAL</t>
+          <t>SER_LU_ECDC_VCJD_ANNUAL</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -15190,7 +15190,7 @@
       </c>
       <c r="AS102" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_HIV_INFECTION_ANNUAL</t>
+          <t>SER_LU_ECDC_VCJD_ANNUAL</t>
         </is>
       </c>
       <c r="AT102" t="n">
@@ -15275,22 +15275,22 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>D173</t>
+          <t>D155</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Rift Valley fever</t>
+          <t>Yersiniosis</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>裂谷热</t>
+          <t>耶尔森菌病</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -15304,17 +15304,17 @@
         </is>
       </c>
       <c r="N103" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="O103" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="R103" t="n">
-        <v>0</v>
+        <v>3.476550157927404</v>
       </c>
       <c r="U103" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_RIFT_ANNUAL</t>
+          <t>SER_LU_ECDC_YERS_ANNUAL</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -15334,7 +15334,7 @@
       </c>
       <c r="AS103" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_RIFT_ANNUAL</t>
+          <t>SER_LU_ECDC_YERS_ANNUAL</t>
         </is>
       </c>
       <c r="AT103" t="n">
@@ -15419,17 +15419,17 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>D203</t>
+          <t>D162</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Crimean-Congo hemorrhagic fever</t>
+          <t>HIV infection</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>克里米亚-刚果出血热</t>
+          <t>人类免疫缺乏病毒感染</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -15448,17 +15448,17 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="O104" t="n">
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="R104" t="n">
-        <v>0</v>
+        <v>24.33585110549182</v>
       </c>
       <c r="U104" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_CCHF_ANNUAL</t>
+          <t>SER_LU_ECDC_HIV_INFECTION_ANNUAL</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -15478,7 +15478,7 @@
       </c>
       <c r="AS104" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_CCHF_ANNUAL</t>
+          <t>SER_LU_ECDC_HIV_INFECTION_ANNUAL</t>
         </is>
       </c>
       <c r="AT104" t="n">
@@ -15563,32 +15563,32 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>D002</t>
+          <t>D173</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Cholera</t>
+          <t>Rift Valley fever</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>霍乱</t>
+          <t>裂谷热</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>2009-01-01</t>
+          <t>2008-01-01</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>2009-01</t>
+          <t>2008-01</t>
         </is>
       </c>
       <c r="N105" t="n">
@@ -15602,7 +15602,7 @@
       </c>
       <c r="U105" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_CHOL_ANNUAL</t>
+          <t>SER_LU_ECDC_RIFT_ANNUAL</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -15622,7 +15622,7 @@
       </c>
       <c r="AS105" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_CHOL_ANNUAL</t>
+          <t>SER_LU_ECDC_RIFT_ANNUAL</t>
         </is>
       </c>
       <c r="AT105" t="n">
@@ -15707,17 +15707,17 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>D005</t>
+          <t>D203</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>AIDS</t>
+          <t>Crimean-Congo hemorrhagic fever</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>艾滋病</t>
+          <t>克里米亚-刚果出血热</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -15727,26 +15727,26 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>2009-01-01</t>
+          <t>2008-01-01</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>2009-01</t>
+          <t>2008-01</t>
         </is>
       </c>
       <c r="N106" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O106" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="R106" t="n">
-        <v>1.806552365429412</v>
+        <v>0</v>
       </c>
       <c r="U106" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_AIDS_ANNUAL</t>
+          <t>SER_LU_ECDC_CCHF_ANNUAL</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -15766,7 +15766,7 @@
       </c>
       <c r="AS106" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_AIDS_ANNUAL</t>
+          <t>SER_LU_ECDC_CCHF_ANNUAL</t>
         </is>
       </c>
       <c r="AT106" t="n">
@@ -15851,22 +15851,22 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>D007</t>
+          <t>D002</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Hepatitis A</t>
+          <t>Cholera</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>甲型肝炎</t>
+          <t>霍乱</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -15880,17 +15880,17 @@
         </is>
       </c>
       <c r="N107" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O107" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R107" t="n">
-        <v>1.00364020301634</v>
+        <v>0</v>
       </c>
       <c r="U107" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_HEPA_ANNUAL</t>
+          <t>SER_LU_ECDC_CHOL_ANNUAL</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -15910,7 +15910,7 @@
       </c>
       <c r="AS107" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_HEPA_ANNUAL</t>
+          <t>SER_LU_ECDC_CHOL_ANNUAL</t>
         </is>
       </c>
       <c r="AT107" t="n">
@@ -15995,17 +15995,17 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>D009</t>
+          <t>D005</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Hepatitis C</t>
+          <t>AIDS</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>丙型肝炎</t>
+          <t>艾滋病</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -16024,17 +16024,17 @@
         </is>
       </c>
       <c r="N108" t="n">
-        <v>55</v>
+        <v>9</v>
       </c>
       <c r="O108" t="n">
-        <v>55</v>
+        <v>9</v>
       </c>
       <c r="R108" t="n">
-        <v>11.04004223317974</v>
+        <v>1.806552365429412</v>
       </c>
       <c r="U108" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_HEPC_ANNUAL</t>
+          <t>SER_LU_ECDC_AIDS_ANNUAL</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -16054,7 +16054,7 @@
       </c>
       <c r="AS108" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_HEPC_ANNUAL</t>
+          <t>SER_LU_ECDC_AIDS_ANNUAL</t>
         </is>
       </c>
       <c r="AT108" t="n">
@@ -16139,17 +16139,17 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>D017</t>
+          <t>D007</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Measles</t>
+          <t>Hepatitis A</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>麻疹</t>
+          <t>甲型肝炎</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -16168,17 +16168,17 @@
         </is>
       </c>
       <c r="N109" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O109" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R109" t="n">
-        <v>0</v>
+        <v>1.00364020301634</v>
       </c>
       <c r="U109" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_MEAS_ANNUAL</t>
+          <t>SER_LU_ECDC_HEPA_ANNUAL</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -16198,7 +16198,7 @@
       </c>
       <c r="AS109" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_MEAS_ANNUAL</t>
+          <t>SER_LU_ECDC_HEPA_ANNUAL</t>
         </is>
       </c>
       <c r="AT109" t="n">
@@ -16283,17 +16283,17 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>D019</t>
+          <t>D009</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Rabies</t>
+          <t>Hepatitis C</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>狂犬病</t>
+          <t>丙型肝炎</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -16312,17 +16312,17 @@
         </is>
       </c>
       <c r="N110" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="O110" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="R110" t="n">
-        <v>0</v>
+        <v>11.04004223317974</v>
       </c>
       <c r="U110" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_RABI_ANNUAL</t>
+          <t>SER_LU_ECDC_HEPC_ANNUAL</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -16342,7 +16342,7 @@
       </c>
       <c r="AS110" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_RABI_ANNUAL</t>
+          <t>SER_LU_ECDC_HEPC_ANNUAL</t>
         </is>
       </c>
       <c r="AT110" t="n">
@@ -16427,17 +16427,17 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>D021</t>
+          <t>D017</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Dengue</t>
+          <t>Measles</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>登革热</t>
+          <t>麻疹</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -16466,7 +16466,7 @@
       </c>
       <c r="U111" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_DENGUE_ANNUAL</t>
+          <t>SER_LU_ECDC_MEAS_ANNUAL</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -16486,7 +16486,7 @@
       </c>
       <c r="AS111" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_DENGUE_ANNUAL</t>
+          <t>SER_LU_ECDC_MEAS_ANNUAL</t>
         </is>
       </c>
       <c r="AT111" t="n">
@@ -16571,22 +16571,22 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>D023</t>
+          <t>D019</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Anthrax</t>
+          <t>Rabies</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>炭疽</t>
+          <t>狂犬病</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -16610,7 +16610,7 @@
       </c>
       <c r="U112" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_ANTH_ANNUAL</t>
+          <t>SER_LU_ECDC_RABI_ANNUAL</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -16630,7 +16630,7 @@
       </c>
       <c r="AS112" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_ANTH_ANNUAL</t>
+          <t>SER_LU_ECDC_RABI_ANNUAL</t>
         </is>
       </c>
       <c r="AT112" t="n">
@@ -16715,22 +16715,22 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>D025</t>
+          <t>D021</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Tuberculosis</t>
+          <t>Dengue</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>肺结核</t>
+          <t>登革热</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -16744,17 +16744,17 @@
         </is>
       </c>
       <c r="N113" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="O113" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="R113" t="n">
-        <v>5.419657096288238</v>
+        <v>0</v>
       </c>
       <c r="U113" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_TUBE_ANNUAL</t>
+          <t>SER_LU_ECDC_DENGUE_ANNUAL</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -16774,7 +16774,7 @@
       </c>
       <c r="AS113" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_TUBE_ANNUAL</t>
+          <t>SER_LU_ECDC_DENGUE_ANNUAL</t>
         </is>
       </c>
       <c r="AT113" t="n">
@@ -16859,17 +16859,17 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>D028</t>
+          <t>D023</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Pertussis</t>
+          <t>Anthrax</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>百日咳</t>
+          <t>炭疽</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -16888,17 +16888,17 @@
         </is>
       </c>
       <c r="N114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R114" t="n">
-        <v>0.200728040603268</v>
+        <v>0</v>
       </c>
       <c r="U114" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_PERT_ANNUAL</t>
+          <t>SER_LU_ECDC_ANTH_ANNUAL</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -16918,7 +16918,7 @@
       </c>
       <c r="AS114" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_PERT_ANNUAL</t>
+          <t>SER_LU_ECDC_ANTH_ANNUAL</t>
         </is>
       </c>
       <c r="AT114" t="n">
@@ -17003,17 +17003,17 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>D032</t>
+          <t>D025</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Brucellosis</t>
+          <t>Tuberculosis</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>布鲁氏菌病</t>
+          <t>肺结核</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -17032,17 +17032,17 @@
         </is>
       </c>
       <c r="N115" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="O115" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="R115" t="n">
-        <v>0</v>
+        <v>5.419657096288238</v>
       </c>
       <c r="U115" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_BRUC_ANNUAL</t>
+          <t>SER_LU_ECDC_TUBE_ANNUAL</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -17062,7 +17062,7 @@
       </c>
       <c r="AS115" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_BRUC_ANNUAL</t>
+          <t>SER_LU_ECDC_TUBE_ANNUAL</t>
         </is>
       </c>
       <c r="AT115" t="n">
@@ -17147,17 +17147,17 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>D033</t>
+          <t>D028</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Gonorrhea</t>
+          <t>Pertussis</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>淋病</t>
+          <t>百日咳</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -17176,17 +17176,17 @@
         </is>
       </c>
       <c r="N116" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="O116" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="R116" t="n">
-        <v>1.204368243619608</v>
+        <v>0.200728040603268</v>
       </c>
       <c r="U116" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_GONO_ANNUAL</t>
+          <t>SER_LU_ECDC_PERT_ANNUAL</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -17206,7 +17206,7 @@
       </c>
       <c r="AS116" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_GONO_ANNUAL</t>
+          <t>SER_LU_ECDC_PERT_ANNUAL</t>
         </is>
       </c>
       <c r="AT116" t="n">
@@ -17291,17 +17291,17 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>D035</t>
+          <t>D032</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Leptospirosis</t>
+          <t>Brucellosis</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>钩端螺旋体病</t>
+          <t>布鲁氏菌病</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -17330,7 +17330,7 @@
       </c>
       <c r="U117" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_LEPT_ANNUAL</t>
+          <t>SER_LU_ECDC_BRUC_ANNUAL</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -17350,7 +17350,7 @@
       </c>
       <c r="AS117" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_LEPT_ANNUAL</t>
+          <t>SER_LU_ECDC_BRUC_ANNUAL</t>
         </is>
       </c>
       <c r="AT117" t="n">
@@ -17435,22 +17435,22 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>D037</t>
+          <t>D033</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Malaria</t>
+          <t>Gonorrhea</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>疟疾</t>
+          <t>淋病</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>Parasitic</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -17464,17 +17464,17 @@
         </is>
       </c>
       <c r="N118" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O118" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R118" t="n">
-        <v>0.6021841218098042</v>
+        <v>1.204368243619608</v>
       </c>
       <c r="U118" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_MALA_ANNUAL</t>
+          <t>SER_LU_ECDC_GONO_ANNUAL</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -17494,7 +17494,7 @@
       </c>
       <c r="AS118" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_MALA_ANNUAL</t>
+          <t>SER_LU_ECDC_GONO_ANNUAL</t>
         </is>
       </c>
       <c r="AT118" t="n">
@@ -17579,22 +17579,22 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>D039</t>
+          <t>D035</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Mumps</t>
+          <t>Leptospirosis</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>流行性腮腺炎</t>
+          <t>钩端螺旋体病</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -17608,17 +17608,17 @@
         </is>
       </c>
       <c r="N119" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="O119" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="R119" t="n">
-        <v>5.018201015081701</v>
+        <v>0</v>
       </c>
       <c r="U119" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_MUMP_ANNUAL</t>
+          <t>SER_LU_ECDC_LEPT_ANNUAL</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -17638,7 +17638,7 @@
       </c>
       <c r="AS119" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_MUMP_ANNUAL</t>
+          <t>SER_LU_ECDC_LEPT_ANNUAL</t>
         </is>
       </c>
       <c r="AT119" t="n">
@@ -17723,17 +17723,17 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>D045</t>
+          <t>D037</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Echinococcosis</t>
+          <t>Malaria</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>包虫病</t>
+          <t>疟疾</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -17752,17 +17752,17 @@
         </is>
       </c>
       <c r="N120" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O120" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R120" t="n">
-        <v>0</v>
+        <v>0.6021841218098042</v>
       </c>
       <c r="U120" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_ECHI_ANNUAL</t>
+          <t>SER_LU_ECDC_MALA_ANNUAL</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -17782,7 +17782,7 @@
       </c>
       <c r="AS120" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_ECHI_ANNUAL</t>
+          <t>SER_LU_ECDC_MALA_ANNUAL</t>
         </is>
       </c>
       <c r="AT120" t="n">
@@ -17867,17 +17867,17 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>D052</t>
+          <t>D039</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Chikungunya</t>
+          <t>Mumps</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>基孔肯雅热</t>
+          <t>流行性腮腺炎</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -17896,17 +17896,17 @@
         </is>
       </c>
       <c r="N121" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="O121" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="R121" t="n">
-        <v>0</v>
+        <v>5.018201015081701</v>
       </c>
       <c r="U121" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_CHIK_ANNUAL</t>
+          <t>SER_LU_ECDC_MUMP_ANNUAL</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -17926,7 +17926,7 @@
       </c>
       <c r="AS121" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_CHIK_ANNUAL</t>
+          <t>SER_LU_ECDC_MUMP_ANNUAL</t>
         </is>
       </c>
       <c r="AT121" t="n">
@@ -18011,17 +18011,17 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>D059</t>
+          <t>D040</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Yellow fever</t>
+          <t>Rubella</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>黄热病</t>
+          <t>风疹</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -18050,7 +18050,7 @@
       </c>
       <c r="U122" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_YELF_ANNUAL</t>
+          <t>SER_LU_ECDC_RUBE_ANNUAL</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -18070,7 +18070,7 @@
       </c>
       <c r="AS122" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_YELF_ANNUAL</t>
+          <t>SER_LU_ECDC_RUBE_ANNUAL</t>
         </is>
       </c>
       <c r="AT122" t="n">
@@ -18155,17 +18155,17 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>D085</t>
+          <t>D045</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Toxoplasmosis</t>
+          <t>Echinococcosis</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>弓形体病</t>
+          <t>包虫病</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -18194,7 +18194,7 @@
       </c>
       <c r="U123" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_TOXO_ANNUAL</t>
+          <t>SER_LU_ECDC_ECHI_ANNUAL</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -18214,7 +18214,7 @@
       </c>
       <c r="AS123" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_TOXO_ANNUAL</t>
+          <t>SER_LU_ECDC_ECHI_ANNUAL</t>
         </is>
       </c>
       <c r="AT123" t="n">
@@ -18299,22 +18299,22 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>D091</t>
+          <t>D052</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Botulism</t>
+          <t>Chikungunya</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>肉毒杆菌中毒</t>
+          <t>基孔肯雅热</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -18338,7 +18338,7 @@
       </c>
       <c r="U124" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_BOTU_ANNUAL</t>
+          <t>SER_LU_ECDC_CHIK_ANNUAL</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -18358,7 +18358,7 @@
       </c>
       <c r="AS124" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_BOTU_ANNUAL</t>
+          <t>SER_LU_ECDC_CHIK_ANNUAL</t>
         </is>
       </c>
       <c r="AT124" t="n">
@@ -18443,22 +18443,22 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>D092</t>
+          <t>D059</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Campylobacteriosis</t>
+          <t>Yellow fever</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>弯曲杆菌病</t>
+          <t>黄热病</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -18472,17 +18472,17 @@
         </is>
       </c>
       <c r="N125" t="n">
-        <v>523</v>
+        <v>0</v>
       </c>
       <c r="O125" t="n">
-        <v>523</v>
+        <v>0</v>
       </c>
       <c r="R125" t="n">
-        <v>104.9807652355092</v>
+        <v>0</v>
       </c>
       <c r="U125" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_CAMP_ANNUAL</t>
+          <t>SER_LU_ECDC_YELF_ANNUAL</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -18502,7 +18502,7 @@
       </c>
       <c r="AS125" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_CAMP_ANNUAL</t>
+          <t>SER_LU_ECDC_YELF_ANNUAL</t>
         </is>
       </c>
       <c r="AT125" t="n">
@@ -18587,17 +18587,17 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>D096</t>
+          <t>D085</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Cryptosporidiosis</t>
+          <t>Toxoplasmosis</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>隐孢子虫病</t>
+          <t>弓形体病</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
@@ -18626,7 +18626,7 @@
       </c>
       <c r="U126" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_CRYP_ANNUAL</t>
+          <t>SER_LU_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -18646,7 +18646,7 @@
       </c>
       <c r="AS126" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_CRYP_ANNUAL</t>
+          <t>SER_LU_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT126" t="n">
@@ -18731,22 +18731,22 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>D099</t>
+          <t>D091</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Giardiasis</t>
+          <t>Botulism</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>贾第虫病</t>
+          <t>肉毒杆菌中毒</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>Parasitic</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -18760,17 +18760,17 @@
         </is>
       </c>
       <c r="N127" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O127" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R127" t="n">
-        <v>0.4014560812065361</v>
+        <v>0</v>
       </c>
       <c r="U127" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_GIAR_ANNUAL</t>
+          <t>SER_LU_ECDC_BOTU_ANNUAL</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -18790,7 +18790,7 @@
       </c>
       <c r="AS127" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_GIAR_ANNUAL</t>
+          <t>SER_LU_ECDC_BOTU_ANNUAL</t>
         </is>
       </c>
       <c r="AT127" t="n">
@@ -18875,17 +18875,17 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>D100</t>
+          <t>D092</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Haemophilus influenzae</t>
+          <t>Campylobacteriosis</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>流感嗜血杆菌</t>
+          <t>弯曲杆菌病</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -18904,17 +18904,17 @@
         </is>
       </c>
       <c r="N128" t="n">
-        <v>0</v>
+        <v>523</v>
       </c>
       <c r="O128" t="n">
-        <v>0</v>
+        <v>523</v>
       </c>
       <c r="R128" t="n">
-        <v>0</v>
+        <v>104.9807652355092</v>
       </c>
       <c r="U128" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_HAEINF_ANNUAL</t>
+          <t>SER_LU_ECDC_CAMP_ANNUAL</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AS128" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_HAEINF_ANNUAL</t>
+          <t>SER_LU_ECDC_CAMP_ANNUAL</t>
         </is>
       </c>
       <c r="AT128" t="n">
@@ -19019,22 +19019,22 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>D102</t>
+          <t>D096</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Hantavirus infection</t>
+          <t>Cryptosporidiosis</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>汉坦病毒感染</t>
+          <t>隐孢子虫病</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Parasitic</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -19048,17 +19048,17 @@
         </is>
       </c>
       <c r="N129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R129" t="n">
-        <v>0.200728040603268</v>
+        <v>0</v>
       </c>
       <c r="U129" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_HANTA_ANNUAL</t>
+          <t>SER_LU_ECDC_CRYP_ANNUAL</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -19078,7 +19078,7 @@
       </c>
       <c r="AS129" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_HANTA_ANNUAL</t>
+          <t>SER_LU_ECDC_CRYP_ANNUAL</t>
         </is>
       </c>
       <c r="AT129" t="n">
@@ -19163,22 +19163,22 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>D105</t>
+          <t>D099</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Shigellosis</t>
+          <t>Giardiasis</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>志贺菌病</t>
+          <t>贾第虫病</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Parasitic</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -19192,17 +19192,17 @@
         </is>
       </c>
       <c r="N130" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="O130" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="R130" t="n">
-        <v>3.010920609049021</v>
+        <v>0.4014560812065361</v>
       </c>
       <c r="U130" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_SHIG_ANNUAL</t>
+          <t>SER_LU_ECDC_GIAR_ANNUAL</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -19222,7 +19222,7 @@
       </c>
       <c r="AS130" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_SHIG_ANNUAL</t>
+          <t>SER_LU_ECDC_GIAR_ANNUAL</t>
         </is>
       </c>
       <c r="AT130" t="n">
@@ -19307,17 +19307,17 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>D107</t>
+          <t>D100</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Legionellosis</t>
+          <t>Haemophilus influenzae</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>军团菌病</t>
+          <t>流感嗜血杆菌</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
@@ -19336,17 +19336,17 @@
         </is>
       </c>
       <c r="N131" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O131" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R131" t="n">
-        <v>1.00364020301634</v>
+        <v>0</v>
       </c>
       <c r="U131" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_LEGI_ANNUAL</t>
+          <t>SER_LU_ECDC_HAEINF_ANNUAL</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -19366,7 +19366,7 @@
       </c>
       <c r="AS131" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_LEGI_ANNUAL</t>
+          <t>SER_LU_ECDC_HAEINF_ANNUAL</t>
         </is>
       </c>
       <c r="AT131" t="n">
@@ -19451,22 +19451,22 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>D108</t>
+          <t>D102</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Listeriosis</t>
+          <t>Hantavirus infection</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>李斯特菌病</t>
+          <t>汉坦病毒感染</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -19480,17 +19480,17 @@
         </is>
       </c>
       <c r="N132" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O132" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R132" t="n">
-        <v>0.6021841218098042</v>
+        <v>0.200728040603268</v>
       </c>
       <c r="U132" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_LIST_ANNUAL</t>
+          <t>SER_LU_ECDC_HANTA_ANNUAL</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -19510,7 +19510,7 @@
       </c>
       <c r="AS132" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_LIST_ANNUAL</t>
+          <t>SER_LU_ECDC_HANTA_ANNUAL</t>
         </is>
       </c>
       <c r="AT132" t="n">
@@ -19595,17 +19595,17 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>D110</t>
+          <t>D105</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Meningococcal disease</t>
+          <t>Shigellosis</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>脑膜炎球菌病</t>
+          <t>志贺菌病</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
@@ -19624,17 +19624,17 @@
         </is>
       </c>
       <c r="N133" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="O133" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="R133" t="n">
-        <v>0.6021841218098042</v>
+        <v>3.010920609049021</v>
       </c>
       <c r="U133" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_MENI_ANNUAL</t>
+          <t>SER_LU_ECDC_SHIG_ANNUAL</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -19654,7 +19654,7 @@
       </c>
       <c r="AS133" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_MENI_ANNUAL</t>
+          <t>SER_LU_ECDC_SHIG_ANNUAL</t>
         </is>
       </c>
       <c r="AT133" t="n">
@@ -19739,17 +19739,17 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>D113</t>
+          <t>D107</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Q fever</t>
+          <t>Legionellosis</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>Q热</t>
+          <t>军团菌病</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
@@ -19768,17 +19768,17 @@
         </is>
       </c>
       <c r="N134" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O134" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R134" t="n">
-        <v>0</v>
+        <v>1.00364020301634</v>
       </c>
       <c r="U134" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_QFEV_ANNUAL</t>
+          <t>SER_LU_ECDC_LEGI_ANNUAL</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -19798,7 +19798,7 @@
       </c>
       <c r="AS134" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_QFEV_ANNUAL</t>
+          <t>SER_LU_ECDC_LEGI_ANNUAL</t>
         </is>
       </c>
       <c r="AT134" t="n">
@@ -19883,17 +19883,17 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>D114</t>
+          <t>D108</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Salmonellosis</t>
+          <t>Listeriosis</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>沙门氏菌病</t>
+          <t>李斯特菌病</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
@@ -19912,17 +19912,17 @@
         </is>
       </c>
       <c r="N135" t="n">
-        <v>162</v>
+        <v>3</v>
       </c>
       <c r="O135" t="n">
-        <v>162</v>
+        <v>3</v>
       </c>
       <c r="R135" t="n">
-        <v>32.51794257772943</v>
+        <v>0.6021841218098042</v>
       </c>
       <c r="U135" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_SALM_ANNUAL</t>
+          <t>SER_LU_ECDC_LIST_ANNUAL</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -19942,7 +19942,7 @@
       </c>
       <c r="AS135" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_SALM_ANNUAL</t>
+          <t>SER_LU_ECDC_LIST_ANNUAL</t>
         </is>
       </c>
       <c r="AT135" t="n">
@@ -20027,17 +20027,17 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>D115</t>
+          <t>D110</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Shiga toxin-producing Escherichia coli infection</t>
+          <t>Meningococcal disease</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>产志贺毒素大肠杆菌感染</t>
+          <t>脑膜炎球菌病</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
@@ -20056,17 +20056,17 @@
         </is>
       </c>
       <c r="N136" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O136" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R136" t="n">
-        <v>1.00364020301634</v>
+        <v>0.6021841218098042</v>
       </c>
       <c r="U136" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_STEC_ANNUAL</t>
+          <t>SER_LU_ECDC_MENI_ANNUAL</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -20086,7 +20086,7 @@
       </c>
       <c r="AS136" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_STEC_ANNUAL</t>
+          <t>SER_LU_ECDC_MENI_ANNUAL</t>
         </is>
       </c>
       <c r="AT136" t="n">
@@ -20171,17 +20171,17 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>D120</t>
+          <t>D113</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Tetanus</t>
+          <t>Q fever</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>破伤风</t>
+          <t>Q热</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
@@ -20210,7 +20210,7 @@
       </c>
       <c r="U137" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_TETA_ANNUAL</t>
+          <t>SER_LU_ECDC_QFEV_ANNUAL</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -20230,7 +20230,7 @@
       </c>
       <c r="AS137" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_TETA_ANNUAL</t>
+          <t>SER_LU_ECDC_QFEV_ANNUAL</t>
         </is>
       </c>
       <c r="AT137" t="n">
@@ -20315,22 +20315,22 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>D122</t>
+          <t>D114</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Trichinellosis</t>
+          <t>Salmonellosis</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>旋毛虫病</t>
+          <t>沙门氏菌病</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>Parasitic</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -20344,17 +20344,17 @@
         </is>
       </c>
       <c r="N138" t="n">
-        <v>0</v>
+        <v>162</v>
       </c>
       <c r="O138" t="n">
-        <v>0</v>
+        <v>162</v>
       </c>
       <c r="R138" t="n">
-        <v>0</v>
+        <v>32.51794257772943</v>
       </c>
       <c r="U138" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_TRIC_ANNUAL</t>
+          <t>SER_LU_ECDC_SALM_ANNUAL</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -20374,7 +20374,7 @@
       </c>
       <c r="AS138" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_TRIC_ANNUAL</t>
+          <t>SER_LU_ECDC_SALM_ANNUAL</t>
         </is>
       </c>
       <c r="AT138" t="n">
@@ -20459,17 +20459,17 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>D123</t>
+          <t>D115</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Tularemia</t>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>土拉菌病</t>
+          <t>产志贺毒素大肠杆菌感染</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
@@ -20488,17 +20488,17 @@
         </is>
       </c>
       <c r="N139" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O139" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R139" t="n">
-        <v>0</v>
+        <v>1.00364020301634</v>
       </c>
       <c r="U139" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_TULA_ANNUAL</t>
+          <t>SER_LU_ECDC_STEC_ANNUAL</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -20518,7 +20518,7 @@
       </c>
       <c r="AS139" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_TULA_ANNUAL</t>
+          <t>SER_LU_ECDC_STEC_ANNUAL</t>
         </is>
       </c>
       <c r="AT139" t="n">
@@ -20603,22 +20603,22 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>D127</t>
+          <t>D120</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Viral hemorrhagic fevers</t>
+          <t>Tetanus</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>病毒性出血热</t>
+          <t>破伤风</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
@@ -20642,7 +20642,7 @@
       </c>
       <c r="U140" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_VHFOTH_ANNUAL</t>
+          <t>SER_LU_ECDC_TETA_ANNUAL</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -20662,7 +20662,7 @@
       </c>
       <c r="AS140" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_VHFOTH_ANNUAL</t>
+          <t>SER_LU_ECDC_TETA_ANNUAL</t>
         </is>
       </c>
       <c r="AT140" t="n">
@@ -20747,22 +20747,22 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>D128</t>
+          <t>D122</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>West Nile virus</t>
+          <t>Trichinellosis</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>西尼罗病毒</t>
+          <t>旋毛虫病</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Parasitic</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
@@ -20786,7 +20786,7 @@
       </c>
       <c r="U141" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_WNF_ANNUAL</t>
+          <t>SER_LU_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -20806,7 +20806,7 @@
       </c>
       <c r="AS141" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_WNF_ANNUAL</t>
+          <t>SER_LU_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AT141" t="n">
@@ -20891,22 +20891,22 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>D144</t>
+          <t>D123</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Creutzfeldt-Jakob disease</t>
+          <t>Tularemia</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>克雅氏病</t>
+          <t>土拉菌病</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>Prion</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -20930,7 +20930,7 @@
       </c>
       <c r="U142" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_VCJD_ANNUAL</t>
+          <t>SER_LU_ECDC_TULA_ANNUAL</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -20950,7 +20950,7 @@
       </c>
       <c r="AS142" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_VCJD_ANNUAL</t>
+          <t>SER_LU_ECDC_TULA_ANNUAL</t>
         </is>
       </c>
       <c r="AT142" t="n">
@@ -21035,22 +21035,22 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>D155</t>
+          <t>D127</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Yersiniosis</t>
+          <t>Viral hemorrhagic fevers</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>耶尔森菌病</t>
+          <t>病毒性出血热</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
@@ -21064,17 +21064,17 @@
         </is>
       </c>
       <c r="N143" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="O143" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="R143" t="n">
-        <v>4.616744933875165</v>
+        <v>0</v>
       </c>
       <c r="U143" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_YERS_ANNUAL</t>
+          <t>SER_LU_ECDC_VHFOTH_ANNUAL</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -21094,7 +21094,7 @@
       </c>
       <c r="AS143" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_YERS_ANNUAL</t>
+          <t>SER_LU_ECDC_VHFOTH_ANNUAL</t>
         </is>
       </c>
       <c r="AT143" t="n">
@@ -21179,17 +21179,17 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>D162</t>
+          <t>D128</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>HIV infection</t>
+          <t>West Nile virus</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>人类免疫缺乏病毒感染</t>
+          <t>西尼罗病毒</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
@@ -21208,17 +21208,17 @@
         </is>
       </c>
       <c r="N144" t="n">
-        <v>139</v>
+        <v>0</v>
       </c>
       <c r="O144" t="n">
-        <v>139</v>
+        <v>0</v>
       </c>
       <c r="R144" t="n">
-        <v>27.90119764385426</v>
+        <v>0</v>
       </c>
       <c r="U144" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_HIV_INFECTION_ANNUAL</t>
+          <t>SER_LU_ECDC_WNF_ANNUAL</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -21238,7 +21238,7 @@
       </c>
       <c r="AS144" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_HIV_INFECTION_ANNUAL</t>
+          <t>SER_LU_ECDC_WNF_ANNUAL</t>
         </is>
       </c>
       <c r="AT144" t="n">
@@ -21323,22 +21323,22 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>D167</t>
+          <t>D144</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>Congenital syphilis</t>
+          <t>Creutzfeldt-Jakob disease</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>先天性梅毒</t>
+          <t>克雅氏病</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Prion</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
@@ -21362,7 +21362,7 @@
       </c>
       <c r="U145" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_CONSYPH_ANNUAL</t>
+          <t>SER_LU_ECDC_VCJD_ANNUAL</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -21382,7 +21382,7 @@
       </c>
       <c r="AS145" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_CONSYPH_ANNUAL</t>
+          <t>SER_LU_ECDC_VCJD_ANNUAL</t>
         </is>
       </c>
       <c r="AT145" t="n">
@@ -21467,22 +21467,22 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>D173</t>
+          <t>D155</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Rift Valley fever</t>
+          <t>Yersiniosis</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>裂谷热</t>
+          <t>耶尔森菌病</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
@@ -21496,17 +21496,17 @@
         </is>
       </c>
       <c r="N146" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="O146" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="R146" t="n">
-        <v>0</v>
+        <v>4.616744933875165</v>
       </c>
       <c r="U146" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_RIFT_ANNUAL</t>
+          <t>SER_LU_ECDC_YERS_ANNUAL</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -21526,7 +21526,7 @@
       </c>
       <c r="AS146" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_RIFT_ANNUAL</t>
+          <t>SER_LU_ECDC_YERS_ANNUAL</t>
         </is>
       </c>
       <c r="AT146" t="n">
@@ -21611,17 +21611,17 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>D203</t>
+          <t>D162</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>Crimean-Congo hemorrhagic fever</t>
+          <t>HIV infection</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>克里米亚-刚果出血热</t>
+          <t>人类免疫缺乏病毒感染</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
@@ -21640,17 +21640,17 @@
         </is>
       </c>
       <c r="N147" t="n">
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="O147" t="n">
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="R147" t="n">
-        <v>0</v>
+        <v>27.90119764385426</v>
       </c>
       <c r="U147" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_CCHF_ANNUAL</t>
+          <t>SER_LU_ECDC_HIV_INFECTION_ANNUAL</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -21670,7 +21670,7 @@
       </c>
       <c r="AS147" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_CCHF_ANNUAL</t>
+          <t>SER_LU_ECDC_HIV_INFECTION_ANNUAL</t>
         </is>
       </c>
       <c r="AT147" t="n">
@@ -21755,17 +21755,17 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>D242</t>
+          <t>D167</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>Lymphogranuloma venereum</t>
+          <t>Congenital syphilis</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>性病性淋巴肉芽肿</t>
+          <t>先天性梅毒</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
@@ -21794,7 +21794,7 @@
       </c>
       <c r="U148" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_LGV_ANNUAL</t>
+          <t>SER_LU_ECDC_CONSYPH_ANNUAL</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -21814,7 +21814,7 @@
       </c>
       <c r="AS148" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_LGV_ANNUAL</t>
+          <t>SER_LU_ECDC_CONSYPH_ANNUAL</t>
         </is>
       </c>
       <c r="AT148" t="n">
@@ -21856,6 +21856,438 @@
         </is>
       </c>
       <c r="BC148" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>lu</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>lu</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>LU</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>D173</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>Rift Valley fever</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>裂谷热</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>2009-01-01</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>2009-01</t>
+        </is>
+      </c>
+      <c r="N149" t="n">
+        <v>0</v>
+      </c>
+      <c r="O149" t="n">
+        <v>0</v>
+      </c>
+      <c r="R149" t="n">
+        <v>0</v>
+      </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>SER_LU_ECDC_RIFT_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO149" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP149" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS149" t="inlineStr">
+        <is>
+          <t>SER_LU_ECDC_RIFT_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT149" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV149" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW149" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Luxembourg Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX149" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY149" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA149" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Luxembourg Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB149" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC149" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>lu</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>lu</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>LU</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>D203</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>Crimean-Congo hemorrhagic fever</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>克里米亚-刚果出血热</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>2009-01-01</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>2009-01</t>
+        </is>
+      </c>
+      <c r="N150" t="n">
+        <v>0</v>
+      </c>
+      <c r="O150" t="n">
+        <v>0</v>
+      </c>
+      <c r="R150" t="n">
+        <v>0</v>
+      </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>SER_LU_ECDC_CCHF_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO150" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP150" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS150" t="inlineStr">
+        <is>
+          <t>SER_LU_ECDC_CCHF_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT150" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV150" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW150" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Luxembourg Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX150" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY150" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA150" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Luxembourg Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB150" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC150" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>lu</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>lu</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>LU</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>D242</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>Lymphogranuloma venereum</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>性病性淋巴肉芽肿</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>2009-01-01</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>2009-01</t>
+        </is>
+      </c>
+      <c r="N151" t="n">
+        <v>0</v>
+      </c>
+      <c r="O151" t="n">
+        <v>0</v>
+      </c>
+      <c r="R151" t="n">
+        <v>0</v>
+      </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>SER_LU_ECDC_LGV_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO151" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP151" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS151" t="inlineStr">
+        <is>
+          <t>SER_LU_ECDC_LGV_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT151" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV151" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW151" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Luxembourg Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX151" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY151" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA151" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Luxembourg Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB151" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC151" t="inlineStr">
         <is>
           <t>official_ecdc_rest_aggregate</t>
         </is>
@@ -21977,7 +22409,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>147</v>
+        <v>150</v>
       </c>
     </row>
     <row r="10">
@@ -21987,7 +22419,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>147</v>
+        <v>150</v>
       </c>
     </row>
     <row r="11">
